--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-716.7%</t>
+          <t>-717.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>501.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-524.2%</t>
+          <t>-541.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-281.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-211.2%</t>
+          <t>-218.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,27 +1308,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.3%</t>
+          <t>-153.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-250.4%</t>
+          <t>-267.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-151.7%</t>
+          <t>-162.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1931"/>
+  <dimension ref="A1:G1930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.858280984156291</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.45832201866015</v>
+        <v>-10.46399069454369</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.051771892962775</v>
+        <v>-1.05403936331619</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.624143327678955</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.55742734220766</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.588329569000245</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.45463109370374</v>
+        <v>-10.46029976958728</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.050295522980211</v>
+        <v>-1.052562993333626</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.624143327678955</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.55742734220766</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.598671256204447</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.6588892690336</v>
+        <v>-10.66455794491714</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.126485595993514</v>
+        <v>-1.128753066346929</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.751782272292944</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.486357172557909</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.592732761792637</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.81952829552197</v>
+        <v>-10.82519697140551</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.186258652104424</v>
+        <v>-1.188526122457839</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.860847069411802</v>
+        <v>-2.86651574529534</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.42540084877103</v>
+        <v>1.421999643240907</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.59585259650338</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.74605846385452</v>
+        <v>-10.75172713973806</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.141499017944023</v>
+        <v>-1.143766488297438</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.787377237744353</v>
+        <v>-2.793045913627891</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.48485444926492</v>
+        <v>1.481453243734798</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.585940098671347</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.92118288124106</v>
+        <v>-10.9268515571246</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.196993564151123</v>
+        <v>-1.199261034504539</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.962501655130897</v>
+        <v>-2.968170331014435</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.394335019580511</v>
+        <v>1.390933814050388</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.581759451473021</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.15563497525555</v>
+        <v>-11.16130365113909</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.297993566658515</v>
+        <v>-1.300261037011931</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.962501655130897</v>
+        <v>-2.968170331014435</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.387115854678915</v>
+        <v>1.383714649148792</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.576573349827146</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.44343881979279</v>
+        <v>-11.44910749567633</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.419787295247387</v>
+        <v>-1.422054765600802</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.250305499668135</v>
+        <v>-3.255974175551673</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.207761357182596</v>
+        <v>1.204360151652473</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.589596871453336</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.67326326695662</v>
+        <v>-11.67893194284015</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.510601284274361</v>
+        <v>-1.512868754627775</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.412953036738296</v>
+        <v>-3.418621712621834</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.111288624779056</v>
+        <v>1.107887419248933</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.587982498360149</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.90529218669288</v>
+        <v>-11.91096086257641</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.600719123539751</v>
+        <v>-1.602986593893166</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.474965733926719</v>
+        <v>-3.480634409810257</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.076774735095117</v>
+        <v>1.073373529564994</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.669554882385293</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.85327667272406</v>
+        <v>-11.8589453486076</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.575922582265824</v>
+        <v>-1.57819005261924</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.474965733926719</v>
+        <v>-3.480634409810257</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.080765070781518</v>
+        <v>1.077363865251395</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.695919122221671</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.99494851444818</v>
+        <v>-12.00061719033172</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.634066545854214</v>
+        <v>-1.63633401620763</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.474965733926719</v>
+        <v>-3.480634409810257</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.079289843882776</v>
+        <v>1.075888638352653</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.787452591003468</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.09385525490746</v>
+        <v>-12.099523930791</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.658575831873053</v>
+        <v>-1.660843302226467</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.573872474385995</v>
+        <v>-3.579541150269532</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.034999209772082</v>
+        <v>1.03159800424196</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.772722406833329</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.89470314767036</v>
+        <v>-11.9003718235539</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.591966122624896</v>
+        <v>-1.59423359297831</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.408549948436181</v>
+        <v>-3.414218624319719</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.121141591695288</v>
+        <v>1.117740386165165</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.781042238678031</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.66885799495095</v>
+        <v>-11.67452667083449</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.492048988500923</v>
+        <v>-1.494316458854339</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.366623272849018</v>
+        <v>-3.372291948732555</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.155876670083794</v>
+        <v>1.152475464553672</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.780724680874853</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.38258318262826</v>
+        <v>-11.38825185851179</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.376399919015786</v>
+        <v>-1.378667389369201</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.366623272849018</v>
+        <v>-3.372291948732555</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.157015814639853</v>
+        <v>1.153614609109731</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.806816390708968</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.43547847067254</v>
+        <v>-11.44114714655608</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.394924260071393</v>
+        <v>-1.397191730424808</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.361667926760572</v>
+        <v>-3.367336602644109</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.162622796455028</v>
+        <v>1.159221590924906</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.86483253167432</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.15156973974379</v>
+        <v>-11.15723841562733</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.275627063461257</v>
+        <v>-1.277894533814672</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.361667926760572</v>
+        <v>-3.367336602644109</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.168356500693665</v>
+        <v>1.164955295163542</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.824458787018081</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.90458248955084</v>
+        <v>-10.91025116543438</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.186569425777941</v>
+        <v>-1.188836896131357</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.11468067656762</v>
+        <v>-3.120349352451157</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.306811588415571</v>
+        <v>1.303410382885449</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.843583517295165</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.64074562234677</v>
+        <v>-10.64641429823031</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.090918160209222</v>
+        <v>-1.093185630562636</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.11468067656762</v>
+        <v>-3.120349352451157</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.296928107102663</v>
+        <v>1.293526901572541</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.86219793649898</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.37350382147837</v>
+        <v>-10.37917249736191</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.985856000361236</v>
+        <v>-0.9881234707146507</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.11468067656762</v>
+        <v>-3.120349352451157</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.29509354660329</v>
+        <v>1.291692341073167</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.880565378374701</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.09769465807789</v>
+        <v>-10.10336333396143</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8758326499745031</v>
+        <v>-0.8781001203279177</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.025661368288886</v>
+        <v>-3.031330044172424</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.348204816597069</v>
+        <v>1.344803611066947</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.896710211159997</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07374111710193</v>
+        <v>-10.07940979298547</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8655827274386261</v>
+        <v>-0.8678501977920408</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.001707827312929</v>
+        <v>-3.007376503196466</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.363245447328137</v>
+        <v>1.359844241798015</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.885191969080527</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.809681178779135</v>
+        <v>-9.815349854662673</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7732190682712594</v>
+        <v>-0.7754865386246745</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.737647888990133</v>
+        <v>-2.74331656487367</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.508421094160063</v>
+        <v>1.50501988862994</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.929133604902479</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.102601555274298</v>
+        <v>-9.108270231157835</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4931742525296254</v>
+        <v>-0.4954417228830406</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.737647888990133</v>
+        <v>-2.74331656487367</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.505634060499762</v>
+        <v>1.502232854969639</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.935255304451482</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.062417256908107</v>
+        <v>-9.068085932791645</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4767569092953079</v>
+        <v>-0.479024379648723</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.697463590623942</v>
+        <v>-2.703132266507479</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.530088263407318</v>
+        <v>1.526687057877195</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.952042608689228</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.982347461370303</v>
+        <v>-8.98801613725384</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.445362169859429</v>
+        <v>-0.4476296402128441</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.617393795086138</v>
+        <v>-2.623062470969675</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.577496961950757</v>
+        <v>1.574095756420634</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.88321128635456</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.748866239140703</v>
+        <v>-8.754534915024241</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.344045252129737</v>
+        <v>-0.3463127224831521</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.383912572856539</v>
+        <v>-2.389581248740077</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.725510124126368</v>
+        <v>1.722108918596246</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.897517979848536</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.56915770899683</v>
+        <v>-8.574826384880367</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2750540503851466</v>
+        <v>-0.2773215207385618</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.326741068693843</v>
+        <v>-2.332409744577381</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.756920816311027</v>
+        <v>1.753519610780904</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.859063105453178</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.436882235365943</v>
+        <v>-8.44255091124948</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2267763741857647</v>
+        <v>-0.2290438445391798</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.194465595062957</v>
+        <v>-2.200134270946494</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.831653587236586</v>
+        <v>1.828252381706463</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.880599651168704</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.246282560692789</v>
+        <v>-8.251951236576327</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1477214436288667</v>
+        <v>-0.1499889139822819</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.003865920389804</v>
+        <v>-2.009534596273341</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.948828452728114</v>
+        <v>1.945427247197991</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.849763429023739</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.997282762009208</v>
+        <v>-8.002951437892746</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.0352151829317755</v>
+        <v>-0.03748265328519063</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.003865920389804</v>
+        <v>-2.009534596273341</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.961734793951773</v>
+        <v>1.958333588421651</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.788812712670397</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.102872751782312</v>
+        <v>-8.10854142766585</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2054271084402362</v>
+        <v>-0.2076945787936513</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.109455910162908</v>
+        <v>-2.115124586046446</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.770404870488692</v>
+        <v>1.767003664958569</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.866303441050655</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.121607653900909</v>
+        <v>-8.127276329784447</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1643767274105885</v>
+        <v>-0.1666441977640036</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.109455910162908</v>
+        <v>-2.115124586046446</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.818949212365778</v>
+        <v>1.815548006835656</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.856214543773561</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.844869479230097</v>
+        <v>-7.850538155113634</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05030244555626862</v>
+        <v>-0.05256991590968374</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.927639249052982</v>
+        <v>-1.93330792493652</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.931418221017728</v>
+        <v>1.928017015487606</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.819447086471953</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.717977072795026</v>
+        <v>-7.723645748678564</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.008259469235718964</v>
+        <v>-0.01052693958913364</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.80641551850145</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.998839678625292</v>
+        <v>1.995438473095169</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.825850573160857</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.5303895648851</v>
+        <v>-7.536058240768638</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.05981492183315851</v>
+        <v>0.05754745147974338</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.80641551850145</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.991879066530199</v>
+        <v>1.988477861000076</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.878803390556169</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.288241171431242</v>
+        <v>-7.293909847314779</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1711366335958449</v>
+        <v>0.1688691632424297</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.80641551850145</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.006341420911342</v>
+        <v>2.002940215381219</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.924432343785567</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.225011799662894</v>
+        <v>-7.230680475546431</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1909605027623793</v>
+        <v>0.1886930324089642</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.80641551850145</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.000873541370537</v>
+        <v>1.997472335840414</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.923933785854798</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.038524107285888</v>
+        <v>-7.044192783169425</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2630536737237588</v>
+        <v>0.2607862033703436</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.614259150240906</v>
+        <v>-1.619927826124444</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.110264250807317</v>
+        <v>2.106863045277195</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.90833453598266</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.017374908382444</v>
+        <v>-7.023043584265982</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2792143315224616</v>
+        <v>0.2769468611690464</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.593109951337463</v>
+        <v>-1.598778627221001</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.130654748386709</v>
+        <v>2.127253542856587</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.844209265380846</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.773609466399</v>
+        <v>-6.779278142282537</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.37250121666289</v>
+        <v>0.3702337463094749</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.593109951337463</v>
+        <v>-1.598778627221001</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.12643545673376</v>
+        <v>2.123034251203637</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.920192090120277</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.509581399205739</v>
+        <v>-6.515250075089277</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4802367574602102</v>
+        <v>0.4779692871067951</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.391244552521509</v>
+        <v>-1.396913228405047</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.249679009943348</v>
+        <v>2.246277804413225</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.922235831341935</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.259731005256665</v>
+        <v>-6.265399681140202</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5729189900235423</v>
+        <v>0.5706515196701272</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.391244552521509</v>
+        <v>-1.396913228405047</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.24242108492705</v>
+        <v>2.239019879396928</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.931838844074249</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.956163516252686</v>
+        <v>-5.961832192136224</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6979451091457824</v>
+        <v>0.6956776387923673</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.391244552521509</v>
+        <v>-1.396913228405047</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.246020208447699</v>
+        <v>2.242619002917576</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.876814768455738</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.882683607400672</v>
+        <v>-5.88835228328421</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7406645787411419</v>
+        <v>0.7383971083877268</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.317764643669495</v>
+        <v>-1.323433319553033</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.303435659813461</v>
+        <v>2.300034454283339</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.869646079695533</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.657650607731849</v>
+        <v>-5.663319283615387</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.829698256224968</v>
+        <v>0.8274307858715528</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.092731644000672</v>
+        <v>-1.09840031988421</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.437475937231052</v>
+        <v>2.434074731700929</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.860498736945828</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.443016230095442</v>
+        <v>-5.44868490597898</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.920246808333848</v>
+        <v>0.9179793379804329</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8780972663642652</v>
+        <v>-0.8837659422478028</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.570951364867213</v>
+        <v>2.567550159337091</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.894695628137535</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.176415873121091</v>
+        <v>-5.182084549004628</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.008081209907384</v>
+        <v>1.005813739553969</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8780972663642652</v>
+        <v>-0.8837659422478028</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.552145623651009</v>
+        <v>2.548744418120886</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.893575741305047</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.93598537631623</v>
+        <v>-4.941654052199768</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.105996485254206</v>
+        <v>1.103729014900791</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6376667695594049</v>
+        <v>-0.6433354454429425</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.698146998358802</v>
+        <v>2.69474579282868</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.917474366430438</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.693194568666785</v>
+        <v>-4.698863244550322</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.207042122148804</v>
+        <v>1.204774651795389</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6376667695594049</v>
+        <v>-0.6433354454429425</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.702076312193622</v>
+        <v>2.6986751066635</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.91820785494272</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.453589477059696</v>
+        <v>-4.459258152943233</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.30356274270898</v>
+        <v>1.301295272355565</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5706188218909104</v>
+        <v>-0.576287497774448</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.742983664712059</v>
+        <v>2.739582459181937</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.944497483565094</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.210933888636532</v>
+        <v>-4.21660256452007</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.397623049298239</v>
+        <v>1.395355578944824</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5706188218909104</v>
+        <v>-0.576287497774448</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.739981735932053</v>
+        <v>2.73658053040193</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.914549808738694</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.990913090599521</v>
+        <v>-3.996581766483059</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.487210405523657</v>
+        <v>1.484942935170242</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4293989768229302</v>
+        <v>-0.4350676527064677</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.826292679983455</v>
+        <v>2.822891474453332</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,45 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009955</v>
+        <v>3.939582570764767</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.791664460694712</v>
+        <v>-3.79733313657825</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.582804040287404</v>
+        <v>1.580536569933989</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4293989768229302</v>
+        <v>-0.4350676527064677</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.842186862785279</v>
-      </c>
-    </row>
-    <row r="1931">
-      <c r="A1931" s="2" t="n">
-        <v>45393</v>
-      </c>
-      <c r="B1931" t="n">
-        <v>3.5789502571949</v>
-      </c>
-      <c r="C1931" t="n">
-        <v>3.100972093319338</v>
-      </c>
-      <c r="D1931" t="n">
-        <v>-3.62587794423605</v>
-      </c>
-      <c r="E1931" t="n">
-        <v>1.650264491311171</v>
-      </c>
-      <c r="F1931" t="n">
-        <v>-0.263612460364268</v>
-      </c>
-      <c r="G1931" t="n">
-        <v>2.942804617100777</v>
+        <v>2.838785657255156</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>118.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-717.3%</t>
+          <t>-716.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-56.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.5%</t>
+          <t>494.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.3%</t>
+          <t>-518.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.5%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-43.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-218.2%</t>
+          <t>-208.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,27 +1308,27 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>-156.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-267.5%</t>
+          <t>-251.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.1%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1930"/>
+  <dimension ref="A1:G1931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43641,10 +43641,10 @@
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.26606255345954</v>
+        <v>1.329091092833469</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.633307125012359</v>
+        <v>3.658518540761931</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43664,10 +43664,10 @@
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.24701080845007</v>
+        <v>1.310039347823998</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.62605117253409</v>
+        <v>3.651262588283662</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43687,10 +43687,10 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.242410788905723</v>
+        <v>1.305439328279652</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.62667717033905</v>
+        <v>3.651888586088622</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43710,10 +43710,10 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.194572426659524</v>
+        <v>1.257600966033453</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.604413879342283</v>
+        <v>3.629625295091854</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43733,10 +43733,10 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.9216579985251232</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.508224717371912</v>
       </c>
       <c r="F1834" t="n">
         <v>1.880332741705669</v>
@@ -43756,10 +43756,10 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.921106198683311</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.506261833297532</v>
       </c>
       <c r="F1835" t="n">
         <v>1.881174505190975</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.8154193107410113</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.443812350748059</v>
       </c>
       <c r="F1836" t="n">
         <v>1.866613431488292</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.8212686918562556</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.446641241920031</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.7730464250091721</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.431432317802864</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.535914933159377</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.371520805560488</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.5409525238869635</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.372113282036861</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.4844828927106667</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.328271811190079</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.4187155026612546</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.302982464300784</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.405180018884545</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.288196302777856</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.3234081184567933</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.245570268561994</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>0.2561990105849157</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.223451942246945</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>0.2601904633801059</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.222873319484261</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2205920995406602</v>
+        <v>-0.1575635601667311</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.028487185821018</v>
+        <v>3.05369860157059</v>
       </c>
       <c r="F1847" t="n">
         <v>1.430838992385719</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4422140330987777</v>
+        <v>-0.3791854937248486</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.939704628996693</v>
+        <v>2.964916044746265</v>
       </c>
       <c r="F1848" t="n">
         <v>1.393312858698349</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6502180914518549</v>
+        <v>-0.5871895520779258</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.861395150209387</v>
+        <v>2.886606565958959</v>
       </c>
       <c r="F1849" t="n">
         <v>1.393312858698349</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9206180541607403</v>
+        <v>-0.8575895147868111</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.748316621463821</v>
+        <v>2.773528037213393</v>
       </c>
       <c r="F1850" t="n">
         <v>1.122912895989464</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.196747892375333</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.630948985484433</v>
       </c>
       <c r="F1851" t="n">
         <v>0.783754518400942</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.524765114102812</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.52008038653221</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4557372966734629</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.081118525011919</v>
+        <v>-2.018089985637991</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305637772577136</v>
+        <v>2.330849188326707</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3507511824338441</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.573503553036016</v>
+        <v>-2.510475013662087</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109790153411229</v>
+        <v>2.1350015691608</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.1416338455902526</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.958683943966089</v>
+        <v>-2.89565540459216</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.954260535852063</v>
+        <v>1.979471951601635</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.1416338455902526</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.302366717192751</v>
+        <v>-3.239338177818823</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.818556550016014</v>
+        <v>1.843767965765586</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.2495398976174708</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.596988528057171</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.696813884326504</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6071902478558189</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.96925117042715</v>
+        <v>-3.906222631053221</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.549681754078772</v>
+        <v>1.574893169828344</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.401056963576938</v>
+        <v>-4.338028424203009</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.363292324286261</v>
+        <v>1.388503740035833</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.727489492444682</v>
+        <v>-4.664460953070753</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.221004087741254</v>
+        <v>1.246215503490826</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.063152139675134</v>
+        <v>-5.000123600301206</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.085319620505039</v>
+        <v>1.11053103625461</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.426778384575448</v>
+        <v>-5.363749845201519</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9463566827791547</v>
+        <v>0.9715680985287265</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.791905767214194</v>
+        <v>-5.728877227840266</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7995602447294878</v>
+        <v>0.8247716604790591</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.220608415970372</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.200494544394873</v>
+        <v>-6.137466005020944</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.634886277871975</v>
+        <v>0.6600976936215468</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.629197193151051</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.613477028535967</v>
+        <v>-6.550448489162037</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4648787166869983</v>
+        <v>0.4900901324365701</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.629197193151051</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.029868902822964</v>
+        <v>-6.966840363449035</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2963160175810766</v>
+        <v>0.3215274333306484</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.629197193151051</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.406545913352809</v>
+        <v>-7.343517373978879</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1559039040378178</v>
+        <v>0.1811153197873896</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.752420735337617</v>
+        <v>-7.689392195963688</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.01365354038958966</v>
+        <v>0.03886495613916141</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.065245534582596</v>
+        <v>-8.002216995208666</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1130714592534008</v>
+        <v>-0.08786004350382948</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.361906876392794</v>
+        <v>-8.298878337018863</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2279570200482719</v>
+        <v>-0.2027456042987001</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.697940328884929</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.795255984503029</v>
+        <v>-8.732227445129098</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4053229678267694</v>
+        <v>-0.3801115520771976</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.697940328884929</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.17825737324566</v>
+        <v>-9.115228833871729</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5586256246454058</v>
+        <v>-0.533414208895834</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.697940328884929</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.490214160043006</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.6808368233929145</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.072925655056207</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-9.849744482547008</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.8192986490964653</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.072925655056207</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.17614451121202</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.9419426406052929</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.39932568372122</v>
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.858280984156291</v>
+        <v>3.500446096776683</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.46399069454369</v>
+        <v>-10.39529347928622</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.05403936331619</v>
+        <v>-1.026560477213203</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.624143327678955</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.55742734220766</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.588329569000245</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.46029976958728</v>
+        <v>-10.39160255432981</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.052562993333626</v>
+        <v>-1.025084107230639</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.624143327678955</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.55742734220766</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.598671256204447</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.66455794491714</v>
+        <v>-10.59586072965967</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.128753066346929</v>
+        <v>-1.101274180243942</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.751782272292944</v>
+        <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.486357172557909</v>
+        <v>1.489758378088031</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.592732761792637</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.82519697140551</v>
+        <v>-10.75649975614804</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.188526122457839</v>
+        <v>-1.161047236354852</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.86651574529534</v>
+        <v>-2.860847069411802</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.421999643240907</v>
+        <v>1.42540084877103</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.59585259650338</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.75172713973806</v>
+        <v>-10.68302992448059</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.143766488297438</v>
+        <v>-1.116287602194451</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.793045913627891</v>
+        <v>-2.787377237744353</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.481453243734798</v>
+        <v>1.48485444926492</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.585940098671347</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.9268515571246</v>
+        <v>-10.85815434186713</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.199261034504539</v>
+        <v>-1.171782148401552</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.968170331014435</v>
+        <v>-2.962501655130897</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.390933814050388</v>
+        <v>1.394335019580511</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.581759451473021</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.16130365113909</v>
+        <v>-11.09260643588162</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.300261037011931</v>
+        <v>-1.272782150908944</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.968170331014435</v>
+        <v>-2.962501655130897</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.383714649148792</v>
+        <v>1.387115854678915</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.576573349827146</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.44910749567633</v>
+        <v>-11.38041028041886</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.422054765600802</v>
+        <v>-1.394575879497815</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.255974175551673</v>
+        <v>-3.250305499668135</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.204360151652473</v>
+        <v>1.207761357182596</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.589596871453336</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.67893194284015</v>
+        <v>-11.61023472758268</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.512868754627775</v>
+        <v>-1.485389868524789</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.418621712621834</v>
+        <v>-3.412953036738296</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.107887419248933</v>
+        <v>1.111288624779056</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.587982498360149</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.91096086257641</v>
+        <v>-11.84226364731895</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.602986593893166</v>
+        <v>-1.575507707790179</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.480634409810257</v>
+        <v>-3.474965733926719</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.073373529564994</v>
+        <v>1.076774735095117</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.669554882385293</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.8589453486076</v>
+        <v>-11.79024813335013</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.57819005261924</v>
+        <v>-1.550711166516253</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.480634409810257</v>
+        <v>-3.474965733926719</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.077363865251395</v>
+        <v>1.080765070781518</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.695919122221671</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.00061719033172</v>
+        <v>-11.93191997507425</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.63633401620763</v>
+        <v>-1.608855130104643</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.480634409810257</v>
+        <v>-3.474965733926719</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.075888638352653</v>
+        <v>1.079289843882776</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.787452591003468</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.099523930791</v>
+        <v>-12.03082671553353</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.660843302226467</v>
+        <v>-1.63336441612348</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.579541150269532</v>
+        <v>-3.573872474385995</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.03159800424196</v>
+        <v>1.034999209772082</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.772722406833329</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.9003718235539</v>
+        <v>-11.83167460829643</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.59423359297831</v>
+        <v>-1.566754706875324</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.414218624319719</v>
+        <v>-3.408549948436181</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.117740386165165</v>
+        <v>1.121141591695288</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.781042238678031</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.67452667083449</v>
+        <v>-11.60582945557702</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.494316458854339</v>
+        <v>-1.466837572751351</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.372291948732555</v>
+        <v>-3.366623272849018</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.152475464553672</v>
+        <v>1.155876670083794</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.780724680874853</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.38825185851179</v>
+        <v>-11.31955464325432</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.378667389369201</v>
+        <v>-1.351188503266214</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.372291948732555</v>
+        <v>-3.366623272849018</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.153614609109731</v>
+        <v>1.157015814639853</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.806816390708968</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.44114714655608</v>
+        <v>-11.37244993129861</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.397191730424808</v>
+        <v>-1.36971284432182</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.367336602644109</v>
+        <v>-3.361667926760572</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.159221590924906</v>
+        <v>1.162622796455028</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.86483253167432</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.15723841562733</v>
+        <v>-11.08854120036986</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.277894533814672</v>
+        <v>-1.250415647711685</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.367336602644109</v>
+        <v>-3.361667926760572</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.164955295163542</v>
+        <v>1.168356500693665</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.824458787018081</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.91025116543438</v>
+        <v>-10.84155395017691</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.188836896131357</v>
+        <v>-1.161358010028369</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.120349352451157</v>
+        <v>-3.11468067656762</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.303410382885449</v>
+        <v>1.306811588415571</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.843583517295165</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.64641429823031</v>
+        <v>-10.57771708297284</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.093185630562636</v>
+        <v>-1.065706744459649</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.120349352451157</v>
+        <v>-3.11468067656762</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.293526901572541</v>
+        <v>1.296928107102663</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.86219793649898</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.37917249736191</v>
+        <v>-10.31047528210444</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9881234707146507</v>
+        <v>-0.9606445846116638</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.120349352451157</v>
+        <v>-3.11468067656762</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.291692341073167</v>
+        <v>1.29509354660329</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.880565378374701</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.10336333396143</v>
+        <v>-10.03466611870396</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8781001203279177</v>
+        <v>-0.85062123422493</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.031330044172424</v>
+        <v>-3.025661368288886</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.344803611066947</v>
+        <v>1.348204816597069</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.896710211159997</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07940979298547</v>
+        <v>-10.010712577728</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8678501977920408</v>
+        <v>-0.8403713116890539</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.007376503196466</v>
+        <v>-3.001707827312929</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.359844241798015</v>
+        <v>1.363245447328137</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.885191969080527</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.815349854662673</v>
+        <v>-9.746652639405202</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7754865386246745</v>
+        <v>-0.7480076525216868</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.74331656487367</v>
+        <v>-2.737647888990133</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.50501988862994</v>
+        <v>1.508421094160063</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.929133604902479</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.108270231157835</v>
+        <v>-9.039573015900364</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4954417228830406</v>
+        <v>-0.4679628367800528</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.74331656487367</v>
+        <v>-2.737647888990133</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.502232854969639</v>
+        <v>1.505634060499762</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.935255304451482</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.068085932791645</v>
+        <v>-8.999388717534174</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.479024379648723</v>
+        <v>-0.4515454935457353</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.703132266507479</v>
+        <v>-2.697463590623942</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.526687057877195</v>
+        <v>1.530088263407318</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.952042608689228</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.98801613725384</v>
+        <v>-8.91931892199637</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4476296402128441</v>
+        <v>-0.4201507541098568</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.623062470969675</v>
+        <v>-2.617393795086138</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.574095756420634</v>
+        <v>1.577496961950757</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.88321128635456</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.754534915024241</v>
+        <v>-8.68583769976677</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3463127224831521</v>
+        <v>-0.3188338363801644</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.389581248740077</v>
+        <v>-2.383912572856539</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.722108918596246</v>
+        <v>1.725510124126368</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.897517979848536</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.574826384880367</v>
+        <v>-8.506129169622897</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2773215207385618</v>
+        <v>-0.2498426346355744</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.332409744577381</v>
+        <v>-2.326741068693843</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.753519610780904</v>
+        <v>1.756920816311027</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.859063105453178</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.44255091124948</v>
+        <v>-8.373853695992009</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2290438445391798</v>
+        <v>-0.2015649584361925</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.200134270946494</v>
+        <v>-2.194465595062957</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.828252381706463</v>
+        <v>1.831653587236586</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.880599651168704</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.251951236576327</v>
+        <v>-8.183254021318856</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1499889139822819</v>
+        <v>-0.1225100278792941</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.009534596273341</v>
+        <v>-2.003865920389804</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.945427247197991</v>
+        <v>1.948828452728114</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.849763429023739</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.002951437892746</v>
+        <v>-7.934254222635275</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03748265328519063</v>
+        <v>-0.01000376718220286</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.009534596273341</v>
+        <v>-2.003865920389804</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.958333588421651</v>
+        <v>1.961734793951773</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.788812712670397</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.10854142766585</v>
+        <v>-8.039844212408379</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2076945787936513</v>
+        <v>-0.1802156926906635</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.115124586046446</v>
+        <v>-2.109455910162908</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.767003664958569</v>
+        <v>1.770404870488692</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.866303441050655</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.127276329784447</v>
+        <v>-8.058579114526976</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1666441977640036</v>
+        <v>-0.1391653116610159</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.115124586046446</v>
+        <v>-2.109455910162908</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.815548006835656</v>
+        <v>1.818949212365778</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.856214543773561</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.850538155113634</v>
+        <v>-7.781840939856163</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05256991590968374</v>
+        <v>-0.02509102980669597</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.93330792493652</v>
+        <v>-1.927639249052982</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.928017015487606</v>
+        <v>1.931418221017728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.819447086471953</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.723645748678564</v>
+        <v>-7.654948533421093</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01052693958913364</v>
+        <v>0.01695194651385368</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.80641551850145</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.995438473095169</v>
+        <v>1.998839678625292</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.825850573160857</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.536058240768638</v>
+        <v>-7.467361025511167</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.05754745147974338</v>
+        <v>0.08502633758273115</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.80641551850145</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.988477861000076</v>
+        <v>1.991879066530199</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.878803390556169</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.293909847314779</v>
+        <v>-7.225212632057309</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1688691632424297</v>
+        <v>0.1963480493454175</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.80641551850145</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.002940215381219</v>
+        <v>2.006341420911342</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.924432343785567</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.230680475546431</v>
+        <v>-7.16198326028896</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1886930324089642</v>
+        <v>0.2161719185119519</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.80641551850145</v>
+        <v>-1.800746842617913</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.997472335840414</v>
+        <v>2.000873541370537</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.923933785854798</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.044192783169425</v>
+        <v>-6.975495567911954</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2607862033703436</v>
+        <v>0.288265089473331</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.619927826124444</v>
+        <v>-1.614259150240906</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.106863045277195</v>
+        <v>2.110264250807317</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.90833453598266</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.023043584265982</v>
+        <v>-6.954346369008511</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2769468611690464</v>
+        <v>0.3044257472720342</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.598778627221001</v>
+        <v>-1.593109951337463</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.127253542856587</v>
+        <v>2.130654748386709</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.844209265380846</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.779278142282537</v>
+        <v>-6.710580927025067</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3702337463094749</v>
+        <v>0.3977126324124627</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.598778627221001</v>
+        <v>-1.593109951337463</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.123034251203637</v>
+        <v>2.12643545673376</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.920192090120277</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.515250075089277</v>
+        <v>-6.446552859831806</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4779692871067951</v>
+        <v>0.5054481732097829</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.396913228405047</v>
+        <v>-1.391244552521509</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246277804413225</v>
+        <v>2.249679009943348</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.922235831341935</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.265399681140202</v>
+        <v>-6.196702465882732</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5706515196701272</v>
+        <v>0.5981304057731145</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.396913228405047</v>
+        <v>-1.391244552521509</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239019879396928</v>
+        <v>2.24242108492705</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.931838844074249</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.961832192136224</v>
+        <v>-5.893134976878753</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6956776387923673</v>
+        <v>0.7231565248953551</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.396913228405047</v>
+        <v>-1.391244552521509</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.242619002917576</v>
+        <v>2.246020208447699</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.876814768455738</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.88835228328421</v>
+        <v>-5.819655068026739</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7383971083877268</v>
+        <v>0.7658759944907141</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.323433319553033</v>
+        <v>-1.317764643669495</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.300034454283339</v>
+        <v>2.303435659813461</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.869646079695533</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.663319283615387</v>
+        <v>-5.594622068357916</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8274307858715528</v>
+        <v>0.8549096719745406</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.09840031988421</v>
+        <v>-1.092731644000672</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.434074731700929</v>
+        <v>2.437475937231052</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.860498736945828</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.44868490597898</v>
+        <v>-5.379987690721509</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9179793379804329</v>
+        <v>0.9454582240834206</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8837659422478028</v>
+        <v>-0.8780972663642652</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.567550159337091</v>
+        <v>2.570951364867213</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.894695628137535</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.182084549004628</v>
+        <v>-5.113387333747157</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.005813739553969</v>
+        <v>1.033292625656957</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8837659422478028</v>
+        <v>-0.8780972663642652</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.548744418120886</v>
+        <v>2.552145623651009</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.893575741305047</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.941654052199768</v>
+        <v>-4.872956836942297</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.103729014900791</v>
+        <v>1.131207901003778</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6433354454429425</v>
+        <v>-0.6376667695594049</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.69474579282868</v>
+        <v>2.698146998358802</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.917474366430438</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.698863244550322</v>
+        <v>-4.630166029292852</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.204774651795389</v>
+        <v>1.232253537898377</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6433354454429425</v>
+        <v>-0.6376667695594049</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.6986751066635</v>
+        <v>2.702076312193622</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.91820785494272</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.459258152943233</v>
+        <v>-4.390560937685763</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.301295272355565</v>
+        <v>1.328774158458552</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.576287497774448</v>
+        <v>-0.5706188218909104</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.739582459181937</v>
+        <v>2.742983664712059</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.944497483565094</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.21660256452007</v>
+        <v>-4.147905349262599</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.395355578944824</v>
+        <v>1.422834465047811</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.576287497774448</v>
+        <v>-0.5706188218909104</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.73658053040193</v>
+        <v>2.739981735932053</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.914549808738694</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.996581766483059</v>
+        <v>-3.927884551225588</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.484942935170242</v>
+        <v>1.51242182127323</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4350676527064677</v>
+        <v>-0.4293989768229302</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.822891474453332</v>
+        <v>2.826292679983455</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,45 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.939582570764767</v>
+        <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.79733313657825</v>
+        <v>-3.728635921320779</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.580536569933989</v>
+        <v>1.608015456036977</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4350676527064677</v>
+        <v>-0.4293989768229302</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.838785657255156</v>
+        <v>2.842186862785279</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="2" t="n">
+        <v>45393</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>3.850854119433273</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>3.100972093319338</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>-3.569120817801409</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>1.672967341885026</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>-0.2698838733035602</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>2.939041769337202</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -801,21 +801,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.2%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.8%</t>
+          <t>496.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.5%</t>
+          <t>-524.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-208.9%</t>
+          <t>-212.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.3%</t>
+          <t>-152.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.0%</t>
+          <t>-256.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>51.3%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>51.4%</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-156.8%</t>
         </is>
       </c>
     </row>
@@ -45340,19 +45340,19 @@
         <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.141493208664449</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.506129169622897</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2498426346355744</v>
+        <v>-0.2613148834984576</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.326741068693843</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.756920816311027</v>
+        <v>1.745448567448144</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.136860695411476</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.373853695992009</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2015649584361925</v>
+        <v>-0.2130372072990756</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.194465595062957</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.831653587236586</v>
+        <v>1.820181338373703</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.139675756099113</v>
       </c>
       <c r="D1906" t="n">
         <v>-8.183254021318856</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1225100278792941</v>
+        <v>-0.1339822767421772</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.003865920389804</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.948828452728114</v>
+        <v>1.937356203865231</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.152582097322772</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.934254222635275</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01000376718220286</v>
+        <v>-0.02147601604508598</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.003865920389804</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.961734793951773</v>
+        <v>1.95026254508889</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.024606167723553</v>
       </c>
       <c r="D1908" t="n">
         <v>-8.039844212408379</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1802156926906635</v>
+        <v>-0.1916879415535471</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.109455910162908</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.770404870488692</v>
+        <v>1.758932621625808</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.073150509600639</v>
       </c>
       <c r="D1909" t="n">
         <v>-8.058579114526976</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1391653116610159</v>
+        <v>-0.1506375605238994</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.109455910162908</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.818949212365778</v>
+        <v>1.807476963502894</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.076529521586634</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.781840939856163</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02509102980669597</v>
+        <v>-0.03656327866957954</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.927639249052982</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.931418221017728</v>
+        <v>1.919945972154845</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.079287784196039</v>
+        <v>3.067815535333156</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.654948533421093</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01695194651385368</v>
+        <v>0.005479697650970117</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.800746842617913</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.998839678625292</v>
+        <v>1.987367429762409</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.072327172100946</v>
+        <v>3.060854923238062</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.467361025511167</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08502633758273115</v>
+        <v>0.07355408871984759</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.800746842617913</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.991879066530199</v>
+        <v>1.980406817667316</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.086789526482089</v>
+        <v>3.075317277619205</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.225212632057309</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1963480493454175</v>
+        <v>0.1848758004825339</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.800746842617913</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.006341420911342</v>
+        <v>1.994869172048459</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.081321646941284</v>
+        <v>3.069849398078401</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.16198326028896</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2161719185119519</v>
+        <v>0.2046996696490684</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.800746842617913</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.000873541370537</v>
+        <v>1.989401292507654</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.078819740951861</v>
+        <v>3.067347492088977</v>
       </c>
       <c r="D1915" t="n">
         <v>-6.975495567911954</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.288265089473331</v>
+        <v>0.2767928406104474</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.614259150240906</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.110264250807317</v>
+        <v>2.098792001944434</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.086520719189187</v>
+        <v>3.075048470326303</v>
       </c>
       <c r="D1916" t="n">
         <v>-6.954346369008511</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3044257472720342</v>
+        <v>0.2929534984091506</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.593109951337463</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.130654748386709</v>
+        <v>2.119182499523825</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.082301427536237</v>
+        <v>3.070829178673354</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.710580927025067</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3977126324124627</v>
+        <v>0.3862403835495791</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.593109951337463</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.12643545673376</v>
+        <v>2.114963207870876</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.084425741456253</v>
+        <v>3.07295349259337</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.446552859831806</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5054481732097829</v>
+        <v>0.4939759243468993</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.391244552521509</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.249679009943348</v>
+        <v>2.238206761080464</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.077167816439955</v>
+        <v>3.065695567577072</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.196702465882732</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5981304057731145</v>
+        <v>0.5866581569102309</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.391244552521509</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.24242108492705</v>
+        <v>2.230948836064166</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.080766939960604</v>
+        <v>3.069294691097721</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.893134976878753</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7231565248953551</v>
+        <v>0.7116842760324715</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.391244552521509</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.246020208447699</v>
+        <v>2.234547959584815</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.094094446015158</v>
+        <v>3.082622197152274</v>
       </c>
       <c r="D1921" t="n">
         <v>-5.819655068026739</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7658759944907141</v>
+        <v>0.7544037456278305</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.317764643669495</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.303435659813461</v>
+        <v>2.291963410950578</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.093114923631455</v>
+        <v>3.081642674768571</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.594622068357916</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8549096719745406</v>
+        <v>0.843437423111657</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.092731644000672</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.437475937231052</v>
+        <v>2.426003688368168</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.097809724685772</v>
+        <v>3.086337475822889</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.379987690721509</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9454582240834206</v>
+        <v>0.9339859752205371</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8780972663642652</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.570951364867213</v>
+        <v>2.55947911600433</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.079003983469568</v>
+        <v>3.067531734606684</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.113387333747157</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.033292625656957</v>
+        <v>1.021820376794073</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8780972663642652</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.552145623651009</v>
+        <v>2.540673374788125</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.080747060094445</v>
+        <v>3.069274811231562</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.872956836942297</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.131207901003778</v>
+        <v>1.119735652140895</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.6376667695594049</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.698146998358802</v>
+        <v>2.686674749495919</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.084676373929265</v>
+        <v>3.073204125066382</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.630166029292852</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.232253537898377</v>
+        <v>1.220781289035493</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.6376667695594049</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.702076312193622</v>
+        <v>2.690604063330739</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.085354957846605</v>
+        <v>3.073882708983722</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.390560937685763</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.328774158458552</v>
+        <v>1.317301909595669</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5706188218909104</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.742983664712059</v>
+        <v>2.731511415849176</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.082353029066599</v>
+        <v>3.070880780203715</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.147905349262599</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.422834465047811</v>
+        <v>1.411362216184928</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5706188218909104</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.739981735932053</v>
+        <v>2.728509487069169</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.083932066077213</v>
+        <v>3.072459817214329</v>
       </c>
       <c r="D1929" t="n">
         <v>-3.927884551225588</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.51242182127323</v>
+        <v>1.500949572410346</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4293989768229302</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.826292679983455</v>
+        <v>2.814820431120571</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.099826248879036</v>
+        <v>3.088354000016153</v>
       </c>
       <c r="D1930" t="n">
         <v>-3.728635921320779</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.608015456036977</v>
+        <v>1.596543207174093</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4293989768229302</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.842186862785279</v>
+        <v>2.830714613922395</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.850854119433273</v>
+        <v>3.807384284005282</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.100972093319338</v>
+        <v>3.089499844456455</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.569120817801409</v>
+        <v>-3.627689836956787</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.672967341885026</v>
+        <v>1.638067485359992</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2698838733035602</v>
+        <v>-0.3284528924589382</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.939041769337202</v>
+        <v>2.892428108981092</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>137.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.2%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.5%</t>
+          <t>499.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-524.3%</t>
+          <t>-542.5%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.9%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-212.4%</t>
+          <t>-218.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.8%</t>
+          <t>-255.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-150.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1931"/>
+  <dimension ref="A1:G1932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43641,10 +43641,10 @@
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.329091092833469</v>
+        <v>1.26606255345954</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.658518540761931</v>
+        <v>3.633307125012359</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43664,10 +43664,10 @@
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.310039347823998</v>
+        <v>1.24701080845007</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.651262588283662</v>
+        <v>3.62605117253409</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43687,10 +43687,10 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.305439328279652</v>
+        <v>1.242410788905723</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.651888586088622</v>
+        <v>3.62667717033905</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43710,10 +43710,10 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.257600966033453</v>
+        <v>1.194572426659524</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.629625295091854</v>
+        <v>3.604413879342283</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43733,10 +43733,10 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9216579985251232</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.508224717371912</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
         <v>1.880332741705669</v>
@@ -43756,10 +43756,10 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.921106198683311</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.506261833297532</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
         <v>1.881174505190975</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.8154193107410113</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.443812350748059</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
         <v>1.866613431488292</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.8212686918562556</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.446641241920031</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7730464250091721</v>
+        <v>0.7100178856352429</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.431432317802864</v>
+        <v>3.406220902053293</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.535914933159377</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.371520805560488</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5409525238869635</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.372113282036861</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4844828927106667</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.328271811190079</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.4187155026612546</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.302982464300784</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.405180018884545</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.288196302777856</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.3234081184567933</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.245570268561994</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.2561990105849157</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.223451942246945</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.2601904633801059</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.222873319484261</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.1575635601667311</v>
+        <v>-0.2205920995406602</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.05369860157059</v>
+        <v>3.028487185821018</v>
       </c>
       <c r="F1847" t="n">
         <v>1.430838992385719</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.3791854937248486</v>
+        <v>-0.4422140330987777</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.964916044746265</v>
+        <v>2.939704628996693</v>
       </c>
       <c r="F1848" t="n">
         <v>1.393312858698349</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.5871895520779258</v>
+        <v>-0.6502180914518549</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.886606565958959</v>
+        <v>2.861395150209387</v>
       </c>
       <c r="F1849" t="n">
         <v>1.393312858698349</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.8575895147868111</v>
+        <v>-0.9206180541607403</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.773528037213393</v>
+        <v>2.748316621463821</v>
       </c>
       <c r="F1850" t="n">
         <v>1.122912895989464</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.196747892375333</v>
+        <v>-1.259776431749262</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.630948985484433</v>
+        <v>2.605737569734861</v>
       </c>
       <c r="F1851" t="n">
         <v>0.783754518400942</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.524765114102812</v>
+        <v>-1.587793653476741</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.52008038653221</v>
+        <v>2.494868970782638</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4557372966734629</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.018089985637991</v>
+        <v>-2.081118525011919</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.330849188326707</v>
+        <v>2.305637772577136</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3507511824338441</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.510475013662087</v>
+        <v>-2.573503553036016</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.1350015691608</v>
+        <v>2.109790153411229</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.1416338455902526</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.89565540459216</v>
+        <v>-2.958683943966089</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.979471951601635</v>
+        <v>1.954260535852063</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.1416338455902526</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.239338177818823</v>
+        <v>-3.302366717192751</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.843767965765586</v>
+        <v>1.818556550016014</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.2495398976174708</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.596988528057171</v>
+        <v>-3.660017067431099</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.696813884326504</v>
+        <v>1.671602468576933</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6071902478558189</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.906222631053221</v>
+        <v>-3.96925117042715</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.574893169828344</v>
+        <v>1.549681754078772</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.338028424203009</v>
+        <v>-4.401056963576938</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.388503740035833</v>
+        <v>1.363292324286261</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.664460953070753</v>
+        <v>-4.727489492444682</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.246215503490826</v>
+        <v>1.221004087741254</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.000123600301206</v>
+        <v>-5.063152139675134</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.11053103625461</v>
+        <v>1.085319620505039</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.363749845201519</v>
+        <v>-5.426778384575448</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9715680985287265</v>
+        <v>0.9463566827791547</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.728877227840266</v>
+        <v>-5.791905767214194</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8247716604790591</v>
+        <v>0.7995602447294878</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.220608415970372</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.137466005020944</v>
+        <v>-6.200494544394873</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6600976936215468</v>
+        <v>0.634886277871975</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.629197193151051</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.550448489162037</v>
+        <v>-6.613477028535967</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4900901324365701</v>
+        <v>0.4648787166869983</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.629197193151051</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.966840363449035</v>
+        <v>-7.029868902822964</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3215274333306484</v>
+        <v>0.2963160175810766</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.629197193151051</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.343517373978879</v>
+        <v>-7.406545913352809</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1811153197873896</v>
+        <v>0.1559039040378178</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.689392195963688</v>
+        <v>-7.752420735337617</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.03886495613916141</v>
+        <v>0.01365354038958966</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.002216995208666</v>
+        <v>-8.065245534582596</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.08786004350382948</v>
+        <v>-0.1130714592534008</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.298878337018863</v>
+        <v>-8.361906876392794</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2027456042987001</v>
+        <v>-0.2279570200482719</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.697940328884929</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.732227445129098</v>
+        <v>-8.795255984503029</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3801115520771976</v>
+        <v>-0.4053229678267694</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.697940328884929</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.115228833871729</v>
+        <v>-9.17825737324566</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.533414208895834</v>
+        <v>-0.5586256246454058</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.697940328884929</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.490214160043006</v>
+        <v>-9.553242699416938</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6808368233929145</v>
+        <v>-0.7060482391424867</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.072925655056207</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.849744482547008</v>
+        <v>-9.912773021920939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8192986490964653</v>
+        <v>-0.8445100648460371</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.072925655056207</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.17614451121202</v>
+        <v>-10.23917305058595</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9419426406052929</v>
+        <v>-0.9671540563548651</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.39932568372122</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.39529347928622</v>
+        <v>-10.45832201866015</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.026560477213203</v>
+        <v>-1.051771892962775</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.618474651795417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.39160255432981</v>
+        <v>-10.45463109370374</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.025084107230639</v>
+        <v>-1.050295522980211</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.618474651795417</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.59586072965967</v>
+        <v>-10.6588892690336</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.101274180243942</v>
+        <v>-1.126485595993514</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.746113596409406</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.75649975614804</v>
+        <v>-10.81952829552197</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.161047236354852</v>
+        <v>-1.186258652104424</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.860847069411802</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.68302992448059</v>
+        <v>-10.74605846385452</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.116287602194451</v>
+        <v>-1.141499017944023</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.787377237744353</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.85815434186713</v>
+        <v>-10.92118288124106</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.171782148401552</v>
+        <v>-1.196993564151123</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.962501655130897</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.09260643588162</v>
+        <v>-11.15563497525555</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.272782150908944</v>
+        <v>-1.297993566658515</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.962501655130897</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.38041028041886</v>
+        <v>-11.44343881979279</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.394575879497815</v>
+        <v>-1.419787295247387</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.250305499668135</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.61023472758268</v>
+        <v>-11.67326326695662</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.485389868524789</v>
+        <v>-1.510601284274361</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.412953036738296</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.84226364731895</v>
+        <v>-11.90529218669288</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.575507707790179</v>
+        <v>-1.600719123539751</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.474965733926719</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.79024813335013</v>
+        <v>-11.85327667272406</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.550711166516253</v>
+        <v>-1.575922582265824</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.474965733926719</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.93191997507425</v>
+        <v>-11.99494851444818</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.608855130104643</v>
+        <v>-1.634066545854214</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.474965733926719</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.03082671553353</v>
+        <v>-12.09385525490746</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.63336441612348</v>
+        <v>-1.658575831873053</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.573872474385995</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.67683797424058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.83167460829643</v>
+        <v>-11.89470314767036</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.566754706875324</v>
+        <v>-1.591966122624896</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.408549948436181</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.60582945557702</v>
+        <v>-11.66885799495095</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.466837572751351</v>
+        <v>-1.492048988500923</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.366623272849018</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.31955464325432</v>
+        <v>-11.38258318262826</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.351188503266214</v>
+        <v>-1.376399919015786</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.366623272849018</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.37244993129861</v>
+        <v>-11.43547847067254</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.36971284432182</v>
+        <v>-1.394924260071393</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.361667926760572</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.08854120036986</v>
+        <v>-11.15156973974379</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.250415647711685</v>
+        <v>-1.275627063461257</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.361667926760572</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.728574354425332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.84155395017691</v>
+        <v>-10.90458248955084</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.161358010028369</v>
+        <v>-1.186569425777941</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.11468067656762</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.57771708297284</v>
+        <v>-10.64074562234677</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.065706744459649</v>
+        <v>-1.090918160209222</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.11468067656762</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.31047528210444</v>
+        <v>-10.37350382147837</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9606445846116638</v>
+        <v>-0.985856000361236</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.11468067656762</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.03466611870396</v>
+        <v>-10.09769465807789</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.85062123422493</v>
+        <v>-0.8758326499745031</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.025661368288886</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.010712577728</v>
+        <v>-10.07374111710193</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8403713116890539</v>
+        <v>-0.8655827274386261</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.001707827312929</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.746652639405202</v>
+        <v>-9.809681178779135</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7480076525216868</v>
+        <v>-0.7732190682712594</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.737647888990133</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.039573015900364</v>
+        <v>-9.102601555274298</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4679628367800528</v>
+        <v>-0.4931742525296254</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.737647888990133</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.999388717534174</v>
+        <v>-9.062417256908107</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4515454935457353</v>
+        <v>-0.4767569092953079</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.697463590623942</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.91931892199637</v>
+        <v>-8.982347461370303</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4201507541098568</v>
+        <v>-0.445362169859429</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.617393795086138</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.68583769976677</v>
+        <v>-8.748866239140703</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3188338363801644</v>
+        <v>-0.344045252129737</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.383912572856539</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.141493208664449</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.506129169622897</v>
+        <v>-8.745837801350373</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2613148834984576</v>
+        <v>-0.3457260873265637</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.326741068693843</v>
+        <v>-2.37229548512247</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.745448567448144</v>
+        <v>1.729588166453851</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.136860695411476</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.373853695992009</v>
+        <v>-8.613562327719485</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2130372072990756</v>
+        <v>-0.2974484111271818</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.194465595062957</v>
+        <v>-2.240020011491584</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.820181338373703</v>
+        <v>1.80432093737941</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.139675756099113</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.183254021318856</v>
+        <v>-8.422962653046332</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1339822767421772</v>
+        <v>-0.2183934805702838</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.003865920389804</v>
+        <v>-2.049420336818431</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.937356203865231</v>
+        <v>1.921495802870938</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.152582097322772</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.934254222635275</v>
+        <v>-8.173962854362751</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.02147601604508598</v>
+        <v>-0.1058872198731926</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.003865920389804</v>
+        <v>-2.049420336818431</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.95026254508889</v>
+        <v>1.934402144094597</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077648</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.024606167723553</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.039844212408379</v>
+        <v>-8.279552844135855</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1916879415535471</v>
+        <v>-0.2760991453816533</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.109455910162908</v>
+        <v>-2.155010326591535</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.758932621625808</v>
+        <v>1.743072220631515</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457906</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.073150509600639</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.058579114526976</v>
+        <v>-8.298287746254452</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1506375605238994</v>
+        <v>-0.2350487643520056</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.109455910162908</v>
+        <v>-2.155010326591535</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.807476963502894</v>
+        <v>1.791616562508602</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.076529521586634</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.781840939856163</v>
+        <v>-8.021549571583639</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03656327866957954</v>
+        <v>-0.1209744824976857</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.927639249052982</v>
+        <v>-1.97319366548161</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.919945972154845</v>
+        <v>1.904085571160552</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.067815535333156</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.654948533421093</v>
+        <v>-7.894657165148569</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.005479697650970117</v>
+        <v>-0.07893150617713607</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.84630125904654</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.987367429762409</v>
+        <v>1.971507028768116</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.060854923238062</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.467361025511167</v>
+        <v>-7.707069657238643</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.07355408871984759</v>
+        <v>-0.0108571151082586</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.84630125904654</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.980406817667316</v>
+        <v>1.964546416673023</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.075317277619205</v>
+        <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.225212632057309</v>
+        <v>-7.464921263784785</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1848758004825339</v>
+        <v>0.1004645966544278</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.84630125904654</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.994869172048459</v>
+        <v>1.979008771054166</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.069849398078401</v>
+        <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.16198326028896</v>
+        <v>-7.401691892016436</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2046996696490684</v>
+        <v>0.1202884658209622</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.800746842617913</v>
+        <v>-1.84630125904654</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.989401292507654</v>
+        <v>1.973540891513361</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.067347492088977</v>
+        <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.975495567911954</v>
+        <v>-7.21520419963943</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2767928406104474</v>
+        <v>0.1923816367823417</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.614259150240906</v>
+        <v>-1.659813566669534</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.098792001944434</v>
+        <v>2.082931600950141</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.075048470326303</v>
+        <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.954346369008511</v>
+        <v>-7.194055000735987</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2929534984091506</v>
+        <v>0.2085422945810445</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.593109951337463</v>
+        <v>-1.63866436776609</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.119182499523825</v>
+        <v>2.103322098529533</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.070829178673354</v>
+        <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.710580927025067</v>
+        <v>-6.950289558752543</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3862403835495791</v>
+        <v>0.3018291797214729</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.593109951337463</v>
+        <v>-1.63866436776609</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.114963207870876</v>
+        <v>2.099102806876584</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.07295349259337</v>
+        <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.446552859831806</v>
+        <v>-6.686261491559282</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4939759243468993</v>
+        <v>0.4095647205187931</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.391244552521509</v>
+        <v>-1.436798968950137</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.238206761080464</v>
+        <v>2.222346360086171</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.065695567577072</v>
+        <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.196702465882732</v>
+        <v>-6.436411097610208</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5866581569102309</v>
+        <v>0.5022469530821252</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.391244552521509</v>
+        <v>-1.436798968950137</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.230948836064166</v>
+        <v>2.215088435069874</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.069294691097721</v>
+        <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.893134976878753</v>
+        <v>-6.132843608606229</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7116842760324715</v>
+        <v>0.6272730722043653</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.391244552521509</v>
+        <v>-1.436798968950137</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.234547959584815</v>
+        <v>2.218687558590522</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.082622197152274</v>
+        <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.819655068026739</v>
+        <v>-6.059363699754215</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7544037456278305</v>
+        <v>0.6699925417997243</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.317764643669495</v>
+        <v>-1.363319060098122</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.291963410950578</v>
+        <v>2.276103009956285</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.081642674768571</v>
+        <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.594622068357916</v>
+        <v>-5.834330700085392</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.843437423111657</v>
+        <v>0.7590262192835509</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.092731644000672</v>
+        <v>-1.138286060429299</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.426003688368168</v>
+        <v>2.410143287373876</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.086337475822889</v>
+        <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.379987690721509</v>
+        <v>-5.619696322448985</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9339859752205371</v>
+        <v>0.8495747713924309</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8780972663642652</v>
+        <v>-0.9236516827928924</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.55947911600433</v>
+        <v>2.543618715010037</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544786</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.067531734606684</v>
+        <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.113387333747157</v>
+        <v>-5.353095965474633</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.021820376794073</v>
+        <v>0.937409172965967</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8780972663642652</v>
+        <v>-0.9236516827928924</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.540673374788125</v>
+        <v>2.524812973793833</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.069274811231562</v>
+        <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.872956836942297</v>
+        <v>-5.112665468669773</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.119735652140895</v>
+        <v>1.035324448312789</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6376667695594049</v>
+        <v>-0.6832211859880322</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.686674749495919</v>
+        <v>2.670814348501626</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.073204125066382</v>
+        <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.630166029292852</v>
+        <v>-4.869874661020328</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.220781289035493</v>
+        <v>1.136370085207387</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6376667695594049</v>
+        <v>-0.6832211859880322</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.690604063330739</v>
+        <v>2.674743662336446</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.073882708983722</v>
+        <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.390560937685763</v>
+        <v>-4.630269569413239</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.317301909595669</v>
+        <v>1.232890705767563</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5706188218909104</v>
+        <v>-0.6161732383195376</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.731511415849176</v>
+        <v>2.715651014854883</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972345</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.070880780203715</v>
+        <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.147905349262599</v>
+        <v>-4.387613980990075</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.411362216184928</v>
+        <v>1.326951012356822</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5706188218909104</v>
+        <v>-0.6161732383195376</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.728509487069169</v>
+        <v>2.712649086074876</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145945</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.072459817214329</v>
+        <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.927884551225588</v>
+        <v>-4.167593182953064</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.500949572410346</v>
+        <v>1.41653836858224</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4293989768229302</v>
+        <v>-0.4749533932515574</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.814820431120571</v>
+        <v>2.798960030126279</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009955</v>
+        <v>3.843270952009957</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.088354000016153</v>
+        <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.728635921320779</v>
+        <v>-3.968344553048255</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.596543207174093</v>
+        <v>1.512132003345987</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4293989768229302</v>
+        <v>-0.4749533932515574</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.830714613922395</v>
+        <v>2.814854212928102</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,45 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.807384284005282</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.089499844456455</v>
+        <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.627689836956787</v>
+        <v>-3.808829449528885</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.638067485359992</v>
+        <v>1.577083889194037</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3284528924589382</v>
+        <v>-0.3154382897321875</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.892428108981092</v>
+        <v>2.911709119480026</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="2" t="n">
+        <v>45394</v>
+      </c>
+      <c r="B1932" t="n">
+        <v>3.57263787030385</v>
+      </c>
+      <c r="C1932" t="n">
+        <v>2.95879492088943</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>-3.808829449528885</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>1.577083889194037</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>-0.3154382897321875</v>
+      </c>
+      <c r="G1932" t="n">
+        <v>2.951858717875798</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,45 +791,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.2%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.7%</t>
+          <t>137.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-716.7%</t>
+          <t>-719.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.6%</t>
+          <t>502.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-542.5%</t>
+          <t>-545.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-282.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-218.5%</t>
+          <t>-219.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.3%</t>
+          <t>-152.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-255.5%</t>
+          <t>-260.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.8%</t>
+          <t>-131.6%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.6588892690336</v>
+        <v>-10.68436521362269</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.126485595993514</v>
+        <v>-1.136675973829149</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.798100881457977</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.458566007058889</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.81952829552197</v>
+        <v>-10.84500424011106</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.186258652104424</v>
+        <v>-1.196449029940059</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.860847069411802</v>
+        <v>-2.912834354460372</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.42540084877103</v>
+        <v>1.394208477741888</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.74605846385452</v>
+        <v>-10.77153440844361</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.141499017944023</v>
+        <v>-1.151689395779659</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.787377237744353</v>
+        <v>-2.839364522792924</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.48485444926492</v>
+        <v>1.453662078235778</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.92118288124106</v>
+        <v>-10.94665882583015</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.196993564151123</v>
+        <v>-1.207183941986759</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.962501655130897</v>
+        <v>-3.014488940179468</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.394335019580511</v>
+        <v>1.363142648551368</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.15563497525555</v>
+        <v>-11.18111091984464</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.297993566658515</v>
+        <v>-1.308183944494151</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.962501655130897</v>
+        <v>-3.014488940179468</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.387115854678915</v>
+        <v>1.355923483649772</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.44343881979279</v>
+        <v>-11.46891476438188</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.419787295247387</v>
+        <v>-1.429977673083023</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.250305499668135</v>
+        <v>-3.302292784716706</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.207761357182596</v>
+        <v>1.176568986153453</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.67326326695662</v>
+        <v>-11.69873921154571</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.510601284274361</v>
+        <v>-1.520791662109996</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.412953036738296</v>
+        <v>-3.464940321786866</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.111288624779056</v>
+        <v>1.080096253749913</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.90529218669288</v>
+        <v>-11.93076813128197</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.600719123539751</v>
+        <v>-1.610909501375386</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.474965733926719</v>
+        <v>-3.52695301897529</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.076774735095117</v>
+        <v>1.045582364065974</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.85327667272406</v>
+        <v>-11.87875261731315</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.575922582265824</v>
+        <v>-1.586112960101461</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.474965733926719</v>
+        <v>-3.52695301897529</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.080765070781518</v>
+        <v>1.049572699752375</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.99494851444818</v>
+        <v>-12.02042445903727</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.634066545854214</v>
+        <v>-1.64425692368985</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.474965733926719</v>
+        <v>-3.52695301897529</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.079289843882776</v>
+        <v>1.048097472853633</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69156815841072</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.09385525490746</v>
+        <v>-12.11933119949655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.658575831873053</v>
+        <v>-1.668766209708689</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.573872474385995</v>
+        <v>-3.625859759434565</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.034999209772082</v>
+        <v>1.00380683874294</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67683797424058</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.89470314767036</v>
+        <v>-11.92017909225945</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.591966122624896</v>
+        <v>-1.602156500460532</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.408549948436181</v>
+        <v>-3.460537233484752</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.121141591695288</v>
+        <v>1.089949220666146</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085282</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.66885799495095</v>
+        <v>-11.69433393954004</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.492048988500923</v>
+        <v>-1.502239366336559</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.366623272849018</v>
+        <v>-3.418610557897588</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.155876670083794</v>
+        <v>1.124684299054652</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282104</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.38258318262826</v>
+        <v>-11.40805912721735</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.376399919015786</v>
+        <v>-1.386590296851422</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.366623272849018</v>
+        <v>-3.418610557897588</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.157015814639853</v>
+        <v>1.125823443610711</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116219</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.43547847067254</v>
+        <v>-11.46095441526163</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.394924260071393</v>
+        <v>-1.405114637907029</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.361667926760572</v>
+        <v>-3.413655211809142</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.162622796455028</v>
+        <v>1.131430425425886</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081571</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.15156973974379</v>
+        <v>-11.17704568433288</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.275627063461257</v>
+        <v>-1.285817441296893</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.361667926760572</v>
+        <v>-3.413655211809142</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.168356500693665</v>
+        <v>1.137164129664523</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425332</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.90458248955084</v>
+        <v>-10.93005843413993</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.186569425777941</v>
+        <v>-1.196759803613578</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.11468067656762</v>
+        <v>-3.16666796161619</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.306811588415571</v>
+        <v>1.275619217386429</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702416</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.64074562234677</v>
+        <v>-10.66622156693586</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.090918160209222</v>
+        <v>-1.101108538044857</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.11468067656762</v>
+        <v>-3.16666796161619</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.296928107102663</v>
+        <v>1.265735736073522</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906231</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.37350382147837</v>
+        <v>-10.39897976606746</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.985856000361236</v>
+        <v>-0.9960463781968723</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.11468067656762</v>
+        <v>-3.16666796161619</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.29509354660329</v>
+        <v>1.263901175574148</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781952</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.09769465807789</v>
+        <v>-10.12317060266698</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8758326499745031</v>
+        <v>-0.8860230278101384</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.025661368288886</v>
+        <v>-3.077648653337456</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.348204816597069</v>
+        <v>1.317012445567927</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567248</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07374111710193</v>
+        <v>-10.09921706169102</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8655827274386261</v>
+        <v>-0.8757731052742623</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.001707827312929</v>
+        <v>-3.053695112361499</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.363245447328137</v>
+        <v>1.332053076298995</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487778</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.809681178779135</v>
+        <v>-9.835157123368225</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7732190682712594</v>
+        <v>-0.7834094461068952</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.737647888990133</v>
+        <v>-2.789635174038703</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.508421094160063</v>
+        <v>1.47722872313092</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.102601555274298</v>
+        <v>-9.128077499863387</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4931742525296254</v>
+        <v>-0.5033646303652612</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.737647888990133</v>
+        <v>-2.789635174038703</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.505634060499762</v>
+        <v>1.47444168947062</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858733</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.062417256908107</v>
+        <v>-9.087893201497197</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4767569092953079</v>
+        <v>-0.4869472871309437</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.697463590623942</v>
+        <v>-2.749450875672512</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.530088263407318</v>
+        <v>1.498895892378176</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096479</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.982347461370303</v>
+        <v>-9.007823405959392</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.445362169859429</v>
+        <v>-0.4555525476950653</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.617393795086138</v>
+        <v>-2.669381080134708</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.577496961950757</v>
+        <v>1.546304590921615</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.748866239140703</v>
+        <v>-8.774342183729793</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.344045252129737</v>
+        <v>-0.3542356299653728</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.383912572856539</v>
+        <v>-2.435899857905109</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.725510124126368</v>
+        <v>1.694317753097226</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.745837801350373</v>
+        <v>-8.771313745939462</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3457260873265637</v>
+        <v>-0.3559164651622</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.37229548512247</v>
+        <v>-2.42428277017104</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.729588166453851</v>
+        <v>1.698395795424709</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.613562327719485</v>
+        <v>-8.639038272308575</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2974484111271818</v>
+        <v>-0.307638788962818</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.240020011491584</v>
+        <v>-2.292007296540154</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.80432093737941</v>
+        <v>1.773128566350268</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575956</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.422962653046332</v>
+        <v>-8.448438597635421</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2183934805702838</v>
+        <v>-0.2285838584059197</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.049420336818431</v>
+        <v>-2.101407621867001</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.921495802870938</v>
+        <v>1.890303431841796</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.173962854362751</v>
+        <v>-8.19943879895184</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1058872198731926</v>
+        <v>-0.1160775977088284</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.049420336818431</v>
+        <v>-2.101407621867001</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.934402144094597</v>
+        <v>1.903209773065455</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077648</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.279552844135855</v>
+        <v>-8.305028788724945</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2760991453816533</v>
+        <v>-0.2862895232172891</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.155010326591535</v>
+        <v>-2.206997611640106</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.743072220631515</v>
+        <v>1.711879849602373</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457906</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.298287746254452</v>
+        <v>-8.323763690843542</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2350487643520056</v>
+        <v>-0.2452391421876414</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.155010326591535</v>
+        <v>-2.206997611640106</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.791616562508602</v>
+        <v>1.76042419147946</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180812</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.021549571583639</v>
+        <v>-8.047025516172729</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1209744824976857</v>
+        <v>-0.1311648603333215</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.97319366548161</v>
+        <v>-2.02518095053018</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.904085571160552</v>
+        <v>1.87289320013141</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.894657165148569</v>
+        <v>-7.920133109737659</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07893150617713607</v>
+        <v>-0.08912188401277188</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.84630125904654</v>
+        <v>-1.89828854409511</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.971507028768116</v>
+        <v>1.940314657738973</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.707069657238643</v>
+        <v>-7.732545601827733</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0108571151082586</v>
+        <v>-0.02104749294389441</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.84630125904654</v>
+        <v>-1.89828854409511</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.964546416673023</v>
+        <v>1.93335404564388</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.464921263784785</v>
+        <v>-7.490397208373874</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1004645966544278</v>
+        <v>0.09027421881879194</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.84630125904654</v>
+        <v>-1.89828854409511</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.979008771054166</v>
+        <v>1.947816400025023</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.401691892016436</v>
+        <v>-7.427167836605526</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1202884658209622</v>
+        <v>0.1100980879853264</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.84630125904654</v>
+        <v>-1.89828854409511</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.973540891513361</v>
+        <v>1.942348520484218</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.21520419963943</v>
+        <v>-7.24068014422852</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1923816367823417</v>
+        <v>0.1821912589467054</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.659813566669534</v>
+        <v>-1.711800851718104</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.082931600950141</v>
+        <v>2.051739229920999</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.194055000735987</v>
+        <v>-7.219530945325077</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2085422945810445</v>
+        <v>0.1983519167454086</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.63866436776609</v>
+        <v>-1.69065165281466</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.103322098529533</v>
+        <v>2.072129727500391</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.950289558752543</v>
+        <v>-6.975765503341632</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3018291797214729</v>
+        <v>0.2916388018858371</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.63866436776609</v>
+        <v>-1.69065165281466</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.099102806876584</v>
+        <v>2.067910435847441</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.686261491559282</v>
+        <v>-6.711737436148372</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4095647205187931</v>
+        <v>0.3993743426831573</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.436798968950137</v>
+        <v>-1.488786253998707</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.222346360086171</v>
+        <v>2.19115398905703</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.436411097610208</v>
+        <v>-6.461887042199297</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5022469530821252</v>
+        <v>0.4920565752464889</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.436798968950137</v>
+        <v>-1.488786253998707</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.215088435069874</v>
+        <v>2.183896064040732</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.132843608606229</v>
+        <v>-6.158319553195319</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6272730722043653</v>
+        <v>0.6170826943687295</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.436798968950137</v>
+        <v>-1.488786253998707</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.218687558590522</v>
+        <v>2.18749518756138</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.059363699754215</v>
+        <v>-6.084839644343305</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6699925417997243</v>
+        <v>0.6598021639640885</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.363319060098122</v>
+        <v>-1.415306345146692</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.276103009956285</v>
+        <v>2.244910638927143</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.834330700085392</v>
+        <v>-5.859806644674482</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7590262192835509</v>
+        <v>0.748835841447915</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.138286060429299</v>
+        <v>-1.190273345477869</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.410143287373876</v>
+        <v>2.378950916344734</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.619696322448985</v>
+        <v>-5.645172267038075</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8495747713924309</v>
+        <v>0.8393843935567951</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9236516827928924</v>
+        <v>-0.9756389678414625</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.543618715010037</v>
+        <v>2.512426343980895</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544786</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.353095965474633</v>
+        <v>-5.378571910063723</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.937409172965967</v>
+        <v>0.9272187951303312</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9236516827928924</v>
+        <v>-0.9756389678414625</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.524812973793833</v>
+        <v>2.493620602764691</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.112665468669773</v>
+        <v>-5.138141413258863</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.035324448312789</v>
+        <v>1.025134070477153</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6832211859880322</v>
+        <v>-0.7352084710366023</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.670814348501626</v>
+        <v>2.639621977472484</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.869874661020328</v>
+        <v>-4.895350605609417</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.136370085207387</v>
+        <v>1.126179707371751</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6832211859880322</v>
+        <v>-0.7352084710366023</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.674743662336446</v>
+        <v>2.643551291307304</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.630269569413239</v>
+        <v>-4.655745514002328</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.232890705767563</v>
+        <v>1.222700327931927</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6161732383195376</v>
+        <v>-0.6681605233681077</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.715651014854883</v>
+        <v>2.684458643825741</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972345</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.387613980990075</v>
+        <v>-4.413089925579165</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.326951012356822</v>
+        <v>1.316760634521186</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6161732383195376</v>
+        <v>-0.6681605233681077</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.712649086074876</v>
+        <v>2.681456715045734</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145945</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.167593182953064</v>
+        <v>-4.193069127542154</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.41653836858224</v>
+        <v>1.406347990746604</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4749533932515574</v>
+        <v>-0.5269406783001275</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.798960030126279</v>
+        <v>2.767767659097137</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009957</v>
+        <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.968344553048255</v>
+        <v>-3.993820497637345</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.512132003345987</v>
+        <v>1.501941625510351</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4749533932515574</v>
+        <v>-0.5269406783001275</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.814854212928102</v>
+        <v>2.78366184189896</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.808829449528885</v>
+        <v>-3.834305394117975</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.577083889194037</v>
+        <v>1.566893511358401</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3154382897321875</v>
+        <v>-0.3674255747807575</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.911709119480026</v>
+        <v>2.880516748450884</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.57263787030385</v>
+        <v>3.767892491959484</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.95879492088943</v>
+        <v>3.151594477291556</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.808829449528885</v>
+        <v>-3.834305394117975</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.577083889194037</v>
+        <v>1.566893511358401</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3154382897321875</v>
+        <v>-0.3674255747807575</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.951858717875798</v>
+        <v>3.144658274277924</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>118.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.9%</t>
+          <t>137.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-719.3%</t>
+          <t>-718.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.3%</t>
+          <t>502.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-545.0%</t>
+          <t>-526.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-282.3%</t>
+          <t>-281.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-219.5%</t>
+          <t>-212.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-152.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.7%</t>
+          <t>-255.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612275</v>
+        <v>3.346417924612274</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213499</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382332</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776683</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.68436521362269</v>
+        <v>-10.67386693925875</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.136675973829149</v>
+        <v>-1.132476664083573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.798100881457977</v>
+        <v>-2.789381891688629</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.458566007058889</v>
+        <v>1.463797400920498</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.84500424011106</v>
+        <v>-10.83450596574711</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.196449029940059</v>
+        <v>-1.192249720194483</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.912834354460372</v>
+        <v>-2.904115364691024</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.394208477741888</v>
+        <v>1.399439871603496</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.77153440844361</v>
+        <v>-10.76103613407967</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.151689395779659</v>
+        <v>-1.147490086034082</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.839364522792924</v>
+        <v>-2.830645533023576</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.453662078235778</v>
+        <v>1.458893472097387</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.94665882583015</v>
+        <v>-10.93616055146621</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.207183941986759</v>
+        <v>-1.202984632241182</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.014488940179468</v>
+        <v>-3.00576995041012</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.363142648551368</v>
+        <v>1.368374042412977</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.18111091984464</v>
+        <v>-11.1706126454807</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.308183944494151</v>
+        <v>-1.303984634748574</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.014488940179468</v>
+        <v>-3.00576995041012</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.355923483649772</v>
+        <v>1.361154877511381</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.46891476438188</v>
+        <v>-11.45841649001794</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.429977673083023</v>
+        <v>-1.425778363337445</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.302292784716706</v>
+        <v>-3.293573794947358</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.176568986153453</v>
+        <v>1.181800380015062</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.69873921154571</v>
+        <v>-11.68824093718176</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.520791662109996</v>
+        <v>-1.51659235236442</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.464940321786866</v>
+        <v>-3.456221332017519</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.080096253749913</v>
+        <v>1.085327647611522</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.93076813128197</v>
+        <v>-11.92026985691802</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.610909501375386</v>
+        <v>-1.606710191629809</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.52695301897529</v>
+        <v>-3.518234029205942</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.045582364065974</v>
+        <v>1.050813757927583</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.87875261731315</v>
+        <v>-11.86825434294921</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.586112960101461</v>
+        <v>-1.581913650355883</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.52695301897529</v>
+        <v>-3.518234029205942</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.049572699752375</v>
+        <v>1.054804093613984</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.02042445903727</v>
+        <v>-12.00992618467333</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.64425692368985</v>
+        <v>-1.640057613944273</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.52695301897529</v>
+        <v>-3.518234029205942</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.048097472853633</v>
+        <v>1.053328866715242</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.11933119949655</v>
+        <v>-12.10883292513261</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.668766209708689</v>
+        <v>-1.664566899963111</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.625859759434565</v>
+        <v>-3.617140769665217</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.00380683874294</v>
+        <v>1.009038232604549</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.67683797424058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.92017909225945</v>
+        <v>-11.90968081789551</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.602156500460532</v>
+        <v>-1.597957190714955</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.460537233484752</v>
+        <v>-3.451818243715404</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.089949220666146</v>
+        <v>1.095180614527754</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.69433393954004</v>
+        <v>-11.6838356651761</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.502239366336559</v>
+        <v>-1.498040056590982</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.418610557897588</v>
+        <v>-3.40989156812824</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.124684299054652</v>
+        <v>1.129915692916261</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.40805912721735</v>
+        <v>-11.3975608528534</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.386590296851422</v>
+        <v>-1.382390987105845</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.418610557897588</v>
+        <v>-3.40989156812824</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.125823443610711</v>
+        <v>1.13105483747232</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.46095441526163</v>
+        <v>-11.45045614089769</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.405114637907029</v>
+        <v>-1.400915328161452</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.413655211809142</v>
+        <v>-3.404936222039794</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.131430425425886</v>
+        <v>1.136661819287495</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.17704568433288</v>
+        <v>-11.16654740996894</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.285817441296893</v>
+        <v>-1.281618131551316</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.413655211809142</v>
+        <v>-3.404936222039794</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.137164129664523</v>
+        <v>1.142395523526131</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.93005843413993</v>
+        <v>-10.91956015977599</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.196759803613578</v>
+        <v>-1.192560493868</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.16666796161619</v>
+        <v>-3.157948971846842</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.275619217386429</v>
+        <v>1.280850611248038</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.66622156693586</v>
+        <v>-10.65572329257192</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.101108538044857</v>
+        <v>-1.09690922829928</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.16666796161619</v>
+        <v>-3.157948971846842</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.265735736073522</v>
+        <v>1.27096712993513</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.39897976606746</v>
+        <v>-10.38848149170352</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9960463781968723</v>
+        <v>-0.9918470684512948</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.16666796161619</v>
+        <v>-3.157948971846842</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.263901175574148</v>
+        <v>1.269132569435756</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12317060266698</v>
+        <v>-10.11267232830304</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8860230278101384</v>
+        <v>-0.8818237180645618</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.077648653337456</v>
+        <v>-3.068929663568109</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.317012445567927</v>
+        <v>1.322243839429535</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.09921706169102</v>
+        <v>-10.08871878732708</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8757731052742623</v>
+        <v>-0.8715737955286849</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.053695112361499</v>
+        <v>-3.044976122592151</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.332053076298995</v>
+        <v>1.337284470160604</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.835157123368225</v>
+        <v>-9.824658849004281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7834094461068952</v>
+        <v>-0.7792101363613182</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.789635174038703</v>
+        <v>-2.780916184269355</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.47722872313092</v>
+        <v>1.482460116992529</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.128077499863387</v>
+        <v>-9.117579225499444</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5033646303652612</v>
+        <v>-0.4991653206196842</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.789635174038703</v>
+        <v>-2.780916184269355</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.47444168947062</v>
+        <v>1.479673083332228</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.087893201497197</v>
+        <v>-9.077394927133254</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4869472871309437</v>
+        <v>-0.4827479773853667</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.749450875672512</v>
+        <v>-2.740731885903164</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.498895892378176</v>
+        <v>1.504127286239784</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.007823405959392</v>
+        <v>-8.997325131595449</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4555525476950653</v>
+        <v>-0.4513532379494878</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.669381080134708</v>
+        <v>-2.66066209036536</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.546304590921615</v>
+        <v>1.551535984783223</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.774342183729793</v>
+        <v>-8.76384390936585</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3542356299653728</v>
+        <v>-0.3500363202197958</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.435899857905109</v>
+        <v>-2.427180868135762</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.694317753097226</v>
+        <v>1.699549146958835</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.771313745939462</v>
+        <v>-8.584135379221976</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3559164651622</v>
+        <v>-0.2810451184752054</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.42428277017104</v>
+        <v>-2.370009363973066</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.698395795424709</v>
+        <v>1.730959839143493</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.639038272308575</v>
+        <v>-8.451859905591089</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.307638788962818</v>
+        <v>-0.2327674422758235</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.292007296540154</v>
+        <v>-2.23773389034218</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.773128566350268</v>
+        <v>1.805692610069052</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.448438597635421</v>
+        <v>-8.261260230917935</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2285838584059197</v>
+        <v>-0.1537125117189255</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.101407621867001</v>
+        <v>-2.047134215669027</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.890303431841796</v>
+        <v>1.92286747556058</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.19943879895184</v>
+        <v>-8.012260432234354</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1160775977088284</v>
+        <v>-0.04120625102183428</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.101407621867001</v>
+        <v>-2.047134215669027</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.903209773065455</v>
+        <v>1.935773816784239</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.305028788724945</v>
+        <v>-8.117850422007459</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2862895232172891</v>
+        <v>-0.2114181765302945</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.206997611640106</v>
+        <v>-2.152724205442131</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.711879849602373</v>
+        <v>1.744443893321158</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.323763690843542</v>
+        <v>-8.136585324126056</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2452391421876414</v>
+        <v>-0.1703677955006473</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.206997611640106</v>
+        <v>-2.152724205442131</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.76042419147946</v>
+        <v>1.792988235198244</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.047025516172729</v>
+        <v>-7.859847149455243</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1311648603333215</v>
+        <v>-0.0562935136463274</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.02518095053018</v>
+        <v>-1.970907544332205</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.87289320013141</v>
+        <v>1.905457243850194</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.920133109737659</v>
+        <v>-7.732954743020173</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08912188401277188</v>
+        <v>-0.0142505373257773</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.89828854409511</v>
+        <v>-1.844015137897136</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.940314657738973</v>
+        <v>1.972878701457758</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.732545601827733</v>
+        <v>-7.545367235110247</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02104749294389441</v>
+        <v>0.05382385374310017</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.89828854409511</v>
+        <v>-1.844015137897136</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.93335404564388</v>
+        <v>1.965918089362665</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.490397208373874</v>
+        <v>-7.303218841656388</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09027421881879194</v>
+        <v>0.1651455655057865</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.89828854409511</v>
+        <v>-1.844015137897136</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.947816400025023</v>
+        <v>1.980380443743808</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.427167836605526</v>
+        <v>-7.23998946988804</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1100980879853264</v>
+        <v>0.1849694346723205</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.89828854409511</v>
+        <v>-1.844015137897136</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.942348520484218</v>
+        <v>1.974912564203003</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262046</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.24068014422852</v>
+        <v>-7.053501777511034</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1821912589467054</v>
+        <v>0.2570626056337</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.711800851718104</v>
+        <v>-1.657527445520129</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.051739229920999</v>
+        <v>2.084303273639784</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.219530945325077</v>
+        <v>-7.032352578607591</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1983519167454086</v>
+        <v>0.2732232634324028</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.69065165281466</v>
+        <v>-1.636378246616686</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.072129727500391</v>
+        <v>2.104693771219175</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.975765503341632</v>
+        <v>-6.788587136624146</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2916388018858371</v>
+        <v>0.3665101485728313</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.69065165281466</v>
+        <v>-1.636378246616686</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.067910435847441</v>
+        <v>2.100474479566226</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.711737436148372</v>
+        <v>-6.524559069430886</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3993743426831573</v>
+        <v>0.4742456893701514</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.488786253998707</v>
+        <v>-1.434512847800733</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.19115398905703</v>
+        <v>2.223718032775814</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.461887042199297</v>
+        <v>-6.274708675481811</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4920565752464889</v>
+        <v>0.5669279219334835</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.488786253998707</v>
+        <v>-1.434512847800733</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.183896064040732</v>
+        <v>2.216460107759516</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.158319553195319</v>
+        <v>-5.971141186477833</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6170826943687295</v>
+        <v>0.6919540410557237</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.488786253998707</v>
+        <v>-1.434512847800733</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.18749518756138</v>
+        <v>2.220059231280165</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.084839644343305</v>
+        <v>-5.897661277625819</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6598021639640885</v>
+        <v>0.7346735106510831</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.415306345146692</v>
+        <v>-1.361032938948718</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.244910638927143</v>
+        <v>2.277474682645927</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.859806644674482</v>
+        <v>-5.672628277956996</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.748835841447915</v>
+        <v>0.8237071881349092</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.190273345477869</v>
+        <v>-1.135999939279895</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.378950916344734</v>
+        <v>2.411514960063518</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.645172267038075</v>
+        <v>-5.457993900320589</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8393843935567951</v>
+        <v>0.9142557402437892</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9756389678414625</v>
+        <v>-0.9213655616434884</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.512426343980895</v>
+        <v>2.544990387699679</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.378571910063723</v>
+        <v>-5.191393543346237</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9272187951303312</v>
+        <v>1.002090141817326</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9756389678414625</v>
+        <v>-0.9213655616434884</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.493620602764691</v>
+        <v>2.526184646483475</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.138141413258863</v>
+        <v>-4.950963046541377</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.025134070477153</v>
+        <v>1.100005417164147</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7352084710366023</v>
+        <v>-0.6809350648386281</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.639621977472484</v>
+        <v>2.672186021191269</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837685</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.895350605609417</v>
+        <v>-4.708172238891931</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.126179707371751</v>
+        <v>1.201051054058746</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7352084710366023</v>
+        <v>-0.6809350648386281</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.643551291307304</v>
+        <v>2.676115335026089</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.655745514002328</v>
+        <v>-4.468567147284842</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.222700327931927</v>
+        <v>1.297571674618921</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6681605233681077</v>
+        <v>-0.6138871171701336</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.684458643825741</v>
+        <v>2.717022687544525</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.413089925579165</v>
+        <v>-4.225911558861679</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.316760634521186</v>
+        <v>1.39163198120818</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6681605233681077</v>
+        <v>-0.6138871171701336</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.681456715045734</v>
+        <v>2.714020758764519</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.193069127542154</v>
+        <v>-4.005890760824668</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.406347990746604</v>
+        <v>1.481219337433599</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5269406783001275</v>
+        <v>-0.4726672721021533</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.767767659097137</v>
+        <v>2.800331702815921</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009955</v>
+        <v>3.843270952009951</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.993820497637345</v>
+        <v>-3.806642130919859</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.501941625510351</v>
+        <v>1.576812972197346</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5269406783001275</v>
+        <v>-0.4726672721021533</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.78366184189896</v>
+        <v>2.816225885617745</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.834305394117975</v>
+        <v>-3.647127027400489</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.566893511358401</v>
+        <v>1.641764858045395</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3674255747807575</v>
+        <v>-0.3131521685827834</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.880516748450884</v>
+        <v>2.913080792169668</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,19 +45981,19 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.767892491959484</v>
+        <v>3.767892491959483</v>
       </c>
       <c r="C1932" t="n">
         <v>3.151594477291556</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.834305394117975</v>
+        <v>-3.647127027400489</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.566893511358401</v>
+        <v>1.641764858045395</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3674255747807575</v>
+        <v>-0.3131521685827834</v>
       </c>
       <c r="G1932" t="n">
         <v>3.144658274277924</v>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,45 +791,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-31.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>138.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-718.2%</t>
+          <t>-716.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.7%</t>
+          <t>593.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-526.3%</t>
+          <t>-567.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.9%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>2037.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-212.0%</t>
+          <t>-228.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-330.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-255.3%</t>
+          <t>-293.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-198.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-131.6%</t>
+          <t>-166.3%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612274</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43681,22 +43681,22 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.242410788905723</v>
+        <v>1.002827137831263</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.62667717033905</v>
+        <v>3.530843709909266</v>
       </c>
       <c r="F1832" t="n">
-        <v>2.216275709213999</v>
+        <v>1.976692058139539</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.459834704618908</v>
+        <v>4.316084513974232</v>
       </c>
     </row>
     <row r="1833">
@@ -43704,22 +43704,22 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.194572426659524</v>
+        <v>0.9549887755850647</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.604413879342283</v>
+        <v>3.508580418912499</v>
       </c>
       <c r="F1833" t="n">
-        <v>2.216275709213999</v>
+        <v>1.976692058139539</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.45670675852062</v>
+        <v>4.312956567875944</v>
       </c>
     </row>
     <row r="1834">
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.6190458080767349</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.387179841192557</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.880332741705669</v>
+        <v>1.640749090631209</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.268117587299011</v>
+        <v>4.124367396654335</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.6184940082349227</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.385216957118176</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.641590854116516</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.123130290607864</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.512807120292623</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.322767474568704</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.627029780413832</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.094218919013701</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.5186565014078673</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.325596365740676</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.627029780413832</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.094708057739576</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.4704342345607838</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.310387441623509</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.578807513566749</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.069854680252992</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.2333027427109887</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.250475929381133</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.578807513566749</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.104795764750534</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.2383403334385752</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.251068405857505</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.634451969833066</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.136759878695662</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.1818707022622785</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.207226935010724</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.577982338656769</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.081624481613622</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.1161033122128664</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.181937588121429</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.577982338656769</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.082642090744091</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.1025678284361568</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.167151426598501</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.577982338656769</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.073270122731847</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.02079592800840513</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.124525392382638</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.605017912062905</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.079574192730767</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.04641317986347254</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.10240706606759</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.605017912062905</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.084339509564469</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.04242172706828234</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.101828443304906</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.609009364858096</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.084559177360823</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2205920995406602</v>
+        <v>-0.4601757506151193</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.028487185821018</v>
+        <v>2.932653725391234</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.430838992385719</v>
+        <v>1.191255341311259</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.975583845382461</v>
+        <v>3.831833654737785</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4422140330987777</v>
+        <v>-0.6817976841732368</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.939704628996693</v>
+        <v>2.843871168566909</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.15372920762389</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>3.809184191124285</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6502180914518549</v>
+        <v>-0.8898017425263141</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.861395150209387</v>
+        <v>2.765561689779604</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.15372920762389</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>3.814076335678211</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9206180541607403</v>
+        <v>-1.160201705235199</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.748316621463821</v>
+        <v>2.652483161034037</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>0.8833292449150043</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.646917814390867</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.259776431749262</v>
+        <v>-1.499360082823721</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.605737569734861</v>
+        <v>2.509904109305078</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.5441708673264822</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.436507087144203</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213499</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.587793653476741</v>
+        <v>-1.827377304551201</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.494868970782638</v>
+        <v>2.399035510352854</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.2161536455990031</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.260035043846484</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416049</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.081118525011919</v>
+        <v>-2.320702176086379</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305637772577136</v>
+        <v>2.209804312147352</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3507511824338441</v>
+        <v>0.1111675313593843</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.348892316355957</v>
+        <v>3.205142125711281</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382332</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.573503553036016</v>
+        <v>-2.813087204110476</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109790153411229</v>
+        <v>2.013956692981445</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.3812174966647124</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.054567691585231</v>
+        <v>2.910817500940555</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.958683943966089</v>
+        <v>-3.198267595040548</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.954260535852063</v>
+        <v>1.858427075422279</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.3812174966647124</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.053110230398095</v>
+        <v>2.909360039753419</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.302366717192751</v>
+        <v>-3.541950368267211</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.818556550016014</v>
+        <v>1.72272308958623</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.4891235486919306</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>2.846385531991704</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.899600718505559</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.575769008147149</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.8467738989302787</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.627901380504953</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.96925117042715</v>
+        <v>-4.20883482150161</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.549681754078772</v>
+        <v>1.453848293648988</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.8467738989302787</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.629674307205212</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207818</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.401056963576938</v>
+        <v>-4.640640614651398</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.363292324286261</v>
+        <v>1.267458863856477</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.9831913953715457</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.534156696807857</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.727489492444682</v>
+        <v>-4.967073143519142</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.221004087741254</v>
+        <v>1.125170627311471</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-1.065659645878694</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.472960521505659</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006537</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.063152139675134</v>
+        <v>-5.302735790749594</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.085319620505039</v>
+        <v>0.9894861600752547</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-1.065659645878694</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.471541113161624</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.426778384575448</v>
+        <v>-5.666362035649907</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9463566827791547</v>
+        <v>0.8505232223493708</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-1.16388128274582</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.41909569127559</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.791905767214194</v>
+        <v>-6.031489418288654</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7995602447294878</v>
+        <v>0.7037267842997035</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.220608415970372</v>
+        <v>-1.460192067044832</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.38431392634669</v>
+        <v>2.240563735702014</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.200494544394873</v>
+        <v>-6.440078195469333</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.634886277871975</v>
+        <v>0.5390528174421911</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.86878084422551</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.137922204053042</v>
+        <v>1.994172013408366</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.613477028535967</v>
+        <v>-6.853060679610427</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4648787166869983</v>
+        <v>0.3690452562572144</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.86878084422551</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.133107636524502</v>
+        <v>1.989357445879826</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.029868902822964</v>
+        <v>-7.269452553897424</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2963160175810766</v>
+        <v>0.2004825571512927</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.86878084422551</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.13110168713338</v>
+        <v>1.987351496488704</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.406545913352809</v>
+        <v>-7.646129564427269</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1559039040378178</v>
+        <v>0.06007044360803393</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.86878084422551</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.141360377802059</v>
+        <v>1.997610187157383</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.752420735337617</v>
+        <v>-7.992004386412077</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.01365354038958966</v>
+        <v>-0.08217992004019425</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.86878084422551</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.137459942947754</v>
+        <v>1.993709752303078</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.065245534582596</v>
+        <v>-8.304829185657056</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1130714592534008</v>
+        <v>-0.2089049196831847</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.86878084422551</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.135864863002755</v>
+        <v>1.992114672358078</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.361906876392794</v>
+        <v>-8.601490527467254</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2279570200482719</v>
+        <v>-0.3237904804780558</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.937523979959389</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.098397957491636</v>
+        <v>1.95464776684696</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.795255984503029</v>
+        <v>-9.034839635577489</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4053229678267694</v>
+        <v>-0.5011564282565533</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.937523979959389</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.094371652957232</v>
+        <v>1.950621462312557</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.17825737324566</v>
+        <v>-9.41784102432012</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5586256246454058</v>
+        <v>-0.6544590850751897</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.937523979959389</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.094269551635648</v>
+        <v>1.950519360990973</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.792826350491397</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.8018816995722706</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.312509306130667</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.728099681259636</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-10.1523566729954</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.9403435252758205</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.312509306130667</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.733449984557687</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.47875670166041</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-1.062987516784649</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.63890933479568</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.545525987315856</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776683</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.45832201866015</v>
+        <v>-10.69790566973461</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.051771892962775</v>
+        <v>-1.147605353392559</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.858058302869877</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.417078357093106</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407497</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.45463109370374</v>
+        <v>-10.6942147447782</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.050295522980211</v>
+        <v>-1.146128983409995</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.858058302869877</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.417078357093106</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611699</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.67386693925875</v>
+        <v>-10.89847292010806</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.132476664083573</v>
+        <v>-1.222319056423298</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.789381891688629</v>
+        <v>-2.985697247483866</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.463797400920498</v>
+        <v>1.346008187443356</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.83450596574711</v>
+        <v>-11.05911194659643</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.192249720194483</v>
+        <v>-1.282092112534208</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.904115364691024</v>
+        <v>-3.100430720486262</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.399439871603496</v>
+        <v>1.281650658126354</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.76103613407967</v>
+        <v>-10.98564211492898</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.147490086034082</v>
+        <v>-1.237332478373807</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.830645533023576</v>
+        <v>-3.026960888818813</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.458893472097387</v>
+        <v>1.341104258620244</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.93616055146621</v>
+        <v>-11.16076653231552</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.202984632241182</v>
+        <v>-1.292827024580907</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.00576995041012</v>
+        <v>-3.202085306205357</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.368374042412977</v>
+        <v>1.250584828935835</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.1706126454807</v>
+        <v>-11.39521862633001</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.303984634748574</v>
+        <v>-1.393827027088299</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.00576995041012</v>
+        <v>-3.202085306205357</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.361154877511381</v>
+        <v>1.243365664034239</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.45841649001794</v>
+        <v>-11.68302247086725</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.425778363337445</v>
+        <v>-1.515620755677171</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.293573794947358</v>
+        <v>-3.489889150742595</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.181800380015062</v>
+        <v>1.06401116653792</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.68824093718176</v>
+        <v>-11.91284691803108</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.51659235236442</v>
+        <v>-1.606434744704145</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.456221332017519</v>
+        <v>-3.652536687812756</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.085327647611522</v>
+        <v>0.9675384341343798</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.92026985691802</v>
+        <v>-12.14487583776734</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.606710191629809</v>
+        <v>-1.696552583969535</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.518234029205942</v>
+        <v>-3.714549385001179</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.050813757927583</v>
+        <v>0.9330245444504408</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792545</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.86825434294921</v>
+        <v>-12.09286032379852</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.581913650355883</v>
+        <v>-1.671756042695609</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.518234029205942</v>
+        <v>-3.714549385001179</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.054804093613984</v>
+        <v>0.9370148801368416</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.00992618467333</v>
+        <v>-12.23453216552264</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.640057613944273</v>
+        <v>-1.729900006283999</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.518234029205942</v>
+        <v>-3.714549385001179</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.053328866715242</v>
+        <v>0.9355396532381</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410721</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.10883292513261</v>
+        <v>-12.33343890598192</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.664566899963111</v>
+        <v>-1.754409292302836</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.617140769665217</v>
+        <v>-3.813456125460454</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.009038232604549</v>
+        <v>0.8912490191274065</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67683797424058</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.90968081789551</v>
+        <v>-12.13428679874482</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.597957190714955</v>
+        <v>-1.68779958305468</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.451818243715404</v>
+        <v>-3.648133599510641</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.095180614527754</v>
+        <v>0.9773914010506117</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085282</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.6838356651761</v>
+        <v>-11.90844164602541</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.498040056590982</v>
+        <v>-1.587882448930706</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.40989156812824</v>
+        <v>-3.606206923923478</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.129915692916261</v>
+        <v>1.012126479439118</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282104</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.3975608528534</v>
+        <v>-11.62216683370271</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.382390987105845</v>
+        <v>-1.47223337944557</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.40989156812824</v>
+        <v>-3.606206923923478</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.13105483747232</v>
+        <v>1.013265623995177</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116219</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.45045614089769</v>
+        <v>-11.675062121747</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.400915328161452</v>
+        <v>-1.490757720501176</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.404936222039794</v>
+        <v>-3.601251577835031</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.136661819287495</v>
+        <v>1.018872605810353</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.16654740996894</v>
+        <v>-11.39115339081825</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.281618131551316</v>
+        <v>-1.371460523891041</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.404936222039794</v>
+        <v>-3.601251577835031</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.142395523526131</v>
+        <v>1.024606310048989</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.91956015977599</v>
+        <v>-11.1441661406253</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.192560493868</v>
+        <v>-1.282402886207725</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.157948971846842</v>
+        <v>-3.354264327642079</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.280850611248038</v>
+        <v>1.163061397770895</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.65572329257192</v>
+        <v>-10.88032927342123</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.09690922829928</v>
+        <v>-1.186751620639005</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.157948971846842</v>
+        <v>-3.354264327642079</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.27096712993513</v>
+        <v>1.153177916457988</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.38848149170352</v>
+        <v>-10.61308747255283</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9918470684512948</v>
+        <v>-1.081689460791019</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.157948971846842</v>
+        <v>-3.354264327642079</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.269132569435756</v>
+        <v>1.151343355958614</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.11267232830304</v>
+        <v>-10.33727830915235</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8818237180645618</v>
+        <v>-0.9716661104042861</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.068929663568109</v>
+        <v>-3.265245019363346</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.322243839429535</v>
+        <v>1.204454625952393</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.08871878732708</v>
+        <v>-10.31332476817639</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8715737955286849</v>
+        <v>-0.9614161878684091</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.044976122592151</v>
+        <v>-3.241291478387388</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.337284470160604</v>
+        <v>1.219495256683461</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.824658849004281</v>
+        <v>-10.04926482985359</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7792101363613182</v>
+        <v>-0.8690525287010429</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.780916184269355</v>
+        <v>-2.977231540064592</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.482460116992529</v>
+        <v>1.364670903515387</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.117579225499444</v>
+        <v>-9.342185206348756</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4991653206196842</v>
+        <v>-0.5890077129594085</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.780916184269355</v>
+        <v>-2.977231540064592</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.479673083332228</v>
+        <v>1.361883869855086</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.077394927133254</v>
+        <v>-9.302000907982565</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4827479773853667</v>
+        <v>-0.5725903697250909</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.740731885903164</v>
+        <v>-2.937047241698401</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.504127286239784</v>
+        <v>1.386338072762642</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.997325131595449</v>
+        <v>-9.221931112444761</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4513532379494878</v>
+        <v>-0.5411956302892125</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.66066209036536</v>
+        <v>-2.856977446160597</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.551535984783223</v>
+        <v>1.433746771306081</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.76384390936585</v>
+        <v>-8.988449890215161</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3500363202197958</v>
+        <v>-0.43987871255952</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.427180868135762</v>
+        <v>-2.623496223930999</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.699549146958835</v>
+        <v>1.581759933481693</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.584135379221976</v>
+        <v>-8.808741360071288</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2810451184752054</v>
+        <v>-0.3708875108149301</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.370009363973066</v>
+        <v>-2.566324719768303</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.730959839143493</v>
+        <v>1.613170625666351</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.451859905591089</v>
+        <v>-8.676465886440401</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2327674422758235</v>
+        <v>-0.3226098346155482</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.23773389034218</v>
+        <v>-2.434049246137417</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.805692610069052</v>
+        <v>1.68790339659191</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.261260230917935</v>
+        <v>-8.485866211767247</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1537125117189255</v>
+        <v>-0.2435549040586498</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.047134215669027</v>
+        <v>-2.243449571464264</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.92286747556058</v>
+        <v>1.805078262083438</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.012260432234354</v>
+        <v>-8.236866413083666</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.04120625102183428</v>
+        <v>-0.131048643361559</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.047134215669027</v>
+        <v>-2.243449571464264</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.935773816784239</v>
+        <v>1.817984603307097</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.117850422007459</v>
+        <v>-8.34245640285677</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2114181765302945</v>
+        <v>-0.3012605688700192</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.152724205442131</v>
+        <v>-2.349039561237368</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.744443893321158</v>
+        <v>1.626654679844016</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.136585324126056</v>
+        <v>-8.361191304975367</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1703677955006473</v>
+        <v>-0.2602101878403715</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.152724205442131</v>
+        <v>-2.349039561237368</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.792988235198244</v>
+        <v>1.675199021721102</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.859847149455243</v>
+        <v>-8.084453130304555</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0562935136463274</v>
+        <v>-0.1461359059860521</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.970907544332205</v>
+        <v>-2.167222900127443</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.905457243850194</v>
+        <v>1.787668030373052</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.732954743020173</v>
+        <v>-8.140769120766286</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0142505373257773</v>
+        <v>-0.1773762884242229</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.844015137897136</v>
+        <v>-2.223538890589175</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.972878701457758</v>
+        <v>1.745164449842534</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.545367235110247</v>
+        <v>-7.95318161285636</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.05382385374310017</v>
+        <v>-0.1093018973553455</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.844015137897136</v>
+        <v>-2.223538890589175</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.965918089362665</v>
+        <v>1.738203837747441</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.303218841656388</v>
+        <v>-7.711033219402502</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1651455655057865</v>
+        <v>0.002019814407340892</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.844015137897136</v>
+        <v>-2.223538890589175</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.980380443743808</v>
+        <v>1.752666192128584</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.23998946988804</v>
+        <v>-7.647803847634154</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1849694346723205</v>
+        <v>0.02184368357387534</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.844015137897136</v>
+        <v>-2.223538890589175</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.974912564203003</v>
+        <v>1.747198312587779</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262046</v>
+        <v>3.828049353262048</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.053501777511034</v>
+        <v>-7.461316155257148</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2570626056337</v>
+        <v>0.09393685453525435</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.657527445520129</v>
+        <v>-2.037051198212169</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.084303273639784</v>
+        <v>1.85658902202456</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.032352578607591</v>
+        <v>-7.440166956353704</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2732232634324028</v>
+        <v>0.1100975123339576</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.636378246616686</v>
+        <v>-2.015901999308725</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.104693771219175</v>
+        <v>1.876979519603952</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.788587136624146</v>
+        <v>-7.19640151437026</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3665101485728313</v>
+        <v>0.2033843974743861</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.636378246616686</v>
+        <v>-2.015901999308725</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.100474479566226</v>
+        <v>1.872760227951002</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.524559069430886</v>
+        <v>-6.932373447177</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4742456893701514</v>
+        <v>0.3111199382717063</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.434512847800733</v>
+        <v>-1.814036600492772</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.223718032775814</v>
+        <v>1.99600378116059</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.274708675481811</v>
+        <v>-6.682523053227925</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5669279219334835</v>
+        <v>0.4038021708350379</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.434512847800733</v>
+        <v>-1.814036600492772</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.216460107759516</v>
+        <v>1.988745856144293</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.971141186477833</v>
+        <v>-6.378955564223946</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6919540410557237</v>
+        <v>0.5288282899572785</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.434512847800733</v>
+        <v>-1.814036600492772</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.220059231280165</v>
+        <v>1.992344979664941</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.897661277625819</v>
+        <v>-6.305475655371932</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7346735106510831</v>
+        <v>0.5715477595526375</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.361032938948718</v>
+        <v>-1.740556691640758</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.277474682645927</v>
+        <v>2.049760431030704</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.672628277956996</v>
+        <v>-6.080442655703109</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8237071881349092</v>
+        <v>0.6605814370364635</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.135999939279895</v>
+        <v>-1.515523691971935</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.411514960063518</v>
+        <v>2.183800708448294</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353078</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.457993900320589</v>
+        <v>-5.865808278066702</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9142557402437892</v>
+        <v>0.751129989145344</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9213655616434884</v>
+        <v>-1.300889314335528</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.544990387699679</v>
+        <v>2.317276136084455</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.191393543346237</v>
+        <v>-5.599207921092351</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.002090141817326</v>
+        <v>0.8389643907188802</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9213655616434884</v>
+        <v>-1.300889314335528</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.526184646483475</v>
+        <v>2.298470394868251</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.950963046541377</v>
+        <v>-5.35877742428749</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.100005417164147</v>
+        <v>0.9368796660657015</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6809350648386281</v>
+        <v>-1.060458817530668</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.672186021191269</v>
+        <v>2.444471769576045</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837685</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.708172238891931</v>
+        <v>-5.115986616638045</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.201051054058746</v>
+        <v>1.0379253029603</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6809350648386281</v>
+        <v>-1.060458817530668</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.676115335026089</v>
+        <v>2.448401083410865</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.468567147284842</v>
+        <v>-4.876381525030956</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.297571674618921</v>
+        <v>1.134445923520476</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6138871171701336</v>
+        <v>-0.9934108698621732</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.717022687544525</v>
+        <v>2.489308435929302</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.225911558861679</v>
+        <v>-4.633725936607792</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.39163198120818</v>
+        <v>1.228506230109735</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6138871171701336</v>
+        <v>-0.9934108698621732</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.714020758764519</v>
+        <v>2.486306507149295</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.005890760824668</v>
+        <v>-4.413705138570782</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.481219337433599</v>
+        <v>1.318093586335153</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4726672721021533</v>
+        <v>-0.852191024794193</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.800331702815921</v>
+        <v>2.572617451200697</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009951</v>
+        <v>3.843270952009955</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.806642130919859</v>
+        <v>-4.214456508665973</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.576812972197346</v>
+        <v>1.4136872210989</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4726672721021533</v>
+        <v>-0.852191024794193</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.816225885617745</v>
+        <v>2.588511634002521</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.647127027400489</v>
+        <v>-4.054941405146603</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.641764858045395</v>
+        <v>1.47863910694695</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3131521685827834</v>
+        <v>-0.692675921274823</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.913080792169668</v>
+        <v>2.685366540554444</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.767892491959483</v>
+        <v>3.448691006751615</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.151594477291556</v>
+        <v>2.804301148820723</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.647127027400489</v>
+        <v>-4.054941405146603</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.641764858045395</v>
+        <v>1.47863910694695</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3131521685827834</v>
+        <v>-0.692675921274823</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.144658274277924</v>
+        <v>2.797364945807091</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>119.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>139.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>593.3%</t>
+          <t>5723.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.1%</t>
+          <t>-544.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2037.6%</t>
+          <t>134.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-228.4%</t>
+          <t>-221.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-330.6%</t>
+          <t>-340.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-39.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-163.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-293.3%</t>
+          <t>-270.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-198.7%</t>
+          <t>-204.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.3%</t>
+          <t>-166.1%</t>
         </is>
       </c>
     </row>
@@ -43687,16 +43687,16 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.002827137831263</v>
+        <v>0.9037096758908947</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.530843709909266</v>
+        <v>3.491196725133119</v>
       </c>
       <c r="F1832" t="n">
-        <v>1.976692058139539</v>
+        <v>1.87757459619917</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.316084513974232</v>
+        <v>4.256614036810011</v>
       </c>
     </row>
     <row r="1833">
@@ -43710,16 +43710,16 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>0.9549887755850647</v>
+        <v>0.8558713136446959</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.508580418912499</v>
+        <v>3.468933434136352</v>
       </c>
       <c r="F1833" t="n">
-        <v>1.976692058139539</v>
+        <v>1.87757459619917</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.312956567875944</v>
+        <v>4.253486090711723</v>
       </c>
     </row>
     <row r="1834">
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.6190458080767349</v>
+        <v>0.5199283461363662</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.387179841192557</v>
+        <v>3.347532856416409</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.640749090631209</v>
+        <v>1.54163162869084</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.124367396654335</v>
+        <v>4.064896919490114</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.6184940082349227</v>
+        <v>0.519376546294554</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.385216957118176</v>
+        <v>3.345569972342029</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.641590854116516</v>
+        <v>1.542473392176147</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.123130290607864</v>
+        <v>4.063659813443643</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.512807120292623</v>
+        <v>0.4136896583522543</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.322767474568704</v>
+        <v>3.283120489792556</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.627029780413832</v>
+        <v>1.527912318473464</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.094218919013701</v>
+        <v>4.03474844184948</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.5186565014078673</v>
+        <v>0.4195390394674987</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.325596365740676</v>
+        <v>3.285949380964528</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.627029780413832</v>
+        <v>1.527912318473464</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.094708057739576</v>
+        <v>4.035237580575354</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4704342345607838</v>
+        <v>0.3713167726204151</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.310387441623509</v>
+        <v>3.270740456847361</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.578807513566749</v>
+        <v>1.47969005162638</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.069854680252992</v>
+        <v>4.010384203088771</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2333027427109887</v>
+        <v>0.13418528077062</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.250475929381133</v>
+        <v>3.210828944604985</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.578807513566749</v>
+        <v>1.47969005162638</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.104795764750534</v>
+        <v>4.045325287586312</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2383403334385752</v>
+        <v>0.1392228714982066</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.251068405857505</v>
+        <v>3.211421421081358</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.634451969833066</v>
+        <v>1.535334507892697</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.136759878695662</v>
+        <v>4.07728940153144</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1818707022622785</v>
+        <v>0.08275324032190978</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.207226935010724</v>
+        <v>3.167579950234576</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.577982338656769</v>
+        <v>1.4788648767164</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.081624481613622</v>
+        <v>4.0221540044494</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1161033122128664</v>
+        <v>0.01698585027249772</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.181937588121429</v>
+        <v>3.142290603345281</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.577982338656769</v>
+        <v>1.4788648767164</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.082642090744091</v>
+        <v>4.02317161357987</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.1025678284361568</v>
+        <v>0.003450366495788115</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.167151426598501</v>
+        <v>3.127504441822353</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.577982338656769</v>
+        <v>1.4788648767164</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.073270122731847</v>
+        <v>4.013799645567626</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.02079592800840513</v>
+        <v>-0.07832153393196356</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.124525392382638</v>
+        <v>3.084878407606491</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.605017912062905</v>
+        <v>1.505900450122537</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.079574192730767</v>
+        <v>4.020103715566545</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.04641317986347254</v>
+        <v>-0.1455306418038412</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.10240706606759</v>
+        <v>3.062760081291442</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.605017912062905</v>
+        <v>1.505900450122537</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.084339509564469</v>
+        <v>4.024869032400249</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.04242172706828234</v>
+        <v>-0.141539189008651</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.101828443304906</v>
+        <v>3.062181458528758</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.609009364858096</v>
+        <v>1.509891902917727</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.084559177360823</v>
+        <v>4.025088700196602</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4601757506151193</v>
+        <v>-0.559293212555488</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.932653725391234</v>
+        <v>2.893006740615087</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.191255341311259</v>
+        <v>1.09213787937089</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.831833654737785</v>
+        <v>3.772363177573564</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6817976841732368</v>
+        <v>-0.7809151461136055</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.843871168566909</v>
+        <v>2.804224183790762</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.15372920762389</v>
+        <v>1.054611745683521</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.809184191124285</v>
+        <v>3.749713713960064</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8898017425263141</v>
+        <v>-0.9889192044666827</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.765561689779604</v>
+        <v>2.725914705003456</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.15372920762389</v>
+        <v>1.054611745683521</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.814076335678211</v>
+        <v>3.754605858513989</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.160201705235199</v>
+        <v>-1.259319167175568</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.652483161034037</v>
+        <v>2.61283617625789</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8833292449150043</v>
+        <v>0.7842117829746356</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.646917814390867</v>
+        <v>3.587447337226646</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.499360082823721</v>
+        <v>-1.59847754476409</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.509904109305078</v>
+        <v>2.47025712452893</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5441708673264822</v>
+        <v>0.4450534053861135</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.436507087144203</v>
+        <v>3.377036609979982</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.827377304551201</v>
+        <v>-1.926494766491569</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.399035510352854</v>
+        <v>2.359388525576707</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2161536455990031</v>
+        <v>0.1170361836586343</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.260035043846484</v>
+        <v>3.200564566682263</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.320702176086379</v>
+        <v>-2.419819638026747</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.209804312147352</v>
+        <v>2.170157327371204</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1111675313593843</v>
+        <v>0.0120500694190156</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.205142125711281</v>
+        <v>3.14567164854706</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.813087204110476</v>
+        <v>-2.912204666050844</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.013956692981445</v>
+        <v>1.974309708205298</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3812174966647124</v>
+        <v>-0.4803349586050811</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.910817500940555</v>
+        <v>2.851347023776334</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.198267595040548</v>
+        <v>-3.297385056980917</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.858427075422279</v>
+        <v>1.818780090646132</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3812174966647124</v>
+        <v>-0.4803349586050811</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.909360039753419</v>
+        <v>2.849889562589198</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.541950368267211</v>
+        <v>-3.64106783020758</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.72272308958623</v>
+        <v>1.683076104810083</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4891235486919306</v>
+        <v>-0.5882410106322993</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.846385531991704</v>
+        <v>2.786915054827483</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.899600718505559</v>
+        <v>-3.998718180445928</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.575769008147149</v>
+        <v>1.536122023371002</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8467738989302787</v>
+        <v>-0.9458913608706474</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.627901380504953</v>
+        <v>2.568430903340732</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.20883482150161</v>
+        <v>-4.307952283441979</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.453848293648988</v>
+        <v>1.414201308872841</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8467738989302787</v>
+        <v>-0.9458913608706474</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.629674307205212</v>
+        <v>2.570203830040991</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.640640614651398</v>
+        <v>-4.739758076591766</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.267458863856477</v>
+        <v>1.22781187908033</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9831913953715457</v>
+        <v>-1.082308857311914</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.534156696807857</v>
+        <v>2.474686219643635</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.967073143519142</v>
+        <v>-5.06619060545951</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.125170627311471</v>
+        <v>1.085523642535323</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.065659645878694</v>
+        <v>-1.164777107819063</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.472960521505659</v>
+        <v>2.413490044341438</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.302735790749594</v>
+        <v>-5.401853252689962</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9894861600752547</v>
+        <v>0.9498391752991076</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.065659645878694</v>
+        <v>-1.164777107819063</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.471541113161624</v>
+        <v>2.412070635997402</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.666362035649907</v>
+        <v>-5.765479497590276</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8505232223493708</v>
+        <v>0.8108762375732237</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.16388128274582</v>
+        <v>-1.262998744686188</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.41909569127559</v>
+        <v>2.359625214111368</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.031489418288654</v>
+        <v>-6.130606880229022</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7037267842997035</v>
+        <v>0.6640797995235563</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.460192067044832</v>
+        <v>-1.559309528985201</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.240563735702014</v>
+        <v>2.181093258537793</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.440078195469333</v>
+        <v>-6.539195657409701</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5390528174421911</v>
+        <v>0.499405832666044</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.86878084422551</v>
+        <v>-1.967898306165879</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.994172013408366</v>
+        <v>1.934701536244145</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.853060679610427</v>
+        <v>-6.952178141550795</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3690452562572144</v>
+        <v>0.3293982714810668</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.86878084422551</v>
+        <v>-1.967898306165879</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.989357445879826</v>
+        <v>1.929886968715605</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.269452553897424</v>
+        <v>-7.368570015837792</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2004825571512927</v>
+        <v>0.1608355723751451</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.86878084422551</v>
+        <v>-1.967898306165879</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.987351496488704</v>
+        <v>1.927881019324483</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.646129564427269</v>
+        <v>-7.745247026367637</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06007044360803393</v>
+        <v>0.02042345883188634</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.86878084422551</v>
+        <v>-1.967898306165879</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.997610187157383</v>
+        <v>1.938139709993162</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.992004386412077</v>
+        <v>-8.091121848352445</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08217992004019425</v>
+        <v>-0.1218269048163418</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.86878084422551</v>
+        <v>-1.967898306165879</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.993709752303078</v>
+        <v>1.934239275138856</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.304829185657056</v>
+        <v>-8.403946647597424</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2089049196831847</v>
+        <v>-0.2485519044593323</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.86878084422551</v>
+        <v>-1.967898306165879</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.992114672358078</v>
+        <v>1.932644195193857</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.601490527467254</v>
+        <v>-8.700607989407622</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3237904804780558</v>
+        <v>-0.3634374652542034</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.937523979959389</v>
+        <v>-2.036641441899758</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.95464776684696</v>
+        <v>1.895177289682739</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.034839635577489</v>
+        <v>-9.133957097517857</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5011564282565533</v>
+        <v>-0.5408034130327004</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.937523979959389</v>
+        <v>-2.036641441899758</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.950621462312557</v>
+        <v>1.891150985148336</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.41784102432012</v>
+        <v>-9.516958486260489</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6544590850751897</v>
+        <v>-0.6941060698513368</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.937523979959389</v>
+        <v>-2.036641441899758</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.950519360990973</v>
+        <v>1.891048883826752</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.792826350491397</v>
+        <v>-9.891943812431766</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8018816995722706</v>
+        <v>-0.8415286843484178</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.312509306130667</v>
+        <v>-2.411626768071035</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.728099681259636</v>
+        <v>1.668629204095415</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.1523566729954</v>
+        <v>-10.25147413493577</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9403435252758205</v>
+        <v>-0.9799905100519686</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.312509306130667</v>
+        <v>-2.411626768071035</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.733449984557687</v>
+        <v>1.673979507393466</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.47875670166041</v>
+        <v>-10.57787416360078</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.062987516784649</v>
+        <v>-1.102634501560796</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.63890933479568</v>
+        <v>-2.738026796736048</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.545525987315856</v>
+        <v>1.486055510151635</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.69790566973461</v>
+        <v>-10.79702313167498</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.147605353392559</v>
+        <v>-1.187252338168706</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.858058302869877</v>
+        <v>-2.957175764810245</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.417078357093106</v>
+        <v>1.357607879928886</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.6942147447782</v>
+        <v>-10.79333220671857</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.146128983409995</v>
+        <v>-1.185775968186142</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.858058302869877</v>
+        <v>-2.957175764810245</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.417078357093106</v>
+        <v>1.357607879928886</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.89847292010806</v>
+        <v>-10.99759038204843</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.222319056423298</v>
+        <v>-1.261966041199445</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.985697247483866</v>
+        <v>-3.084814709424234</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.346008187443356</v>
+        <v>1.286537710279135</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.05911194659643</v>
+        <v>-11.1582294085368</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.282092112534208</v>
+        <v>-1.321739097310355</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.100430720486262</v>
+        <v>-3.19954818242663</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.281650658126354</v>
+        <v>1.222180180962133</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.98564211492898</v>
+        <v>-11.08475957686935</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.237332478373807</v>
+        <v>-1.276979463149954</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.026960888818813</v>
+        <v>-3.126078350759181</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.341104258620244</v>
+        <v>1.281633781456023</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16076653231552</v>
+        <v>-11.25988399425589</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.292827024580907</v>
+        <v>-1.332474009357055</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.202085306205357</v>
+        <v>-3.301202768145725</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.250584828935835</v>
+        <v>1.191114351771614</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.39521862633001</v>
+        <v>-11.49433608827038</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.393827027088299</v>
+        <v>-1.433474011864446</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.202085306205357</v>
+        <v>-3.301202768145725</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.243365664034239</v>
+        <v>1.183895186870018</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.68302247086725</v>
+        <v>-11.78213993280762</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.515620755677171</v>
+        <v>-1.555267740453318</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.489889150742595</v>
+        <v>-3.589006612682963</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.06401116653792</v>
+        <v>1.004540689373699</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.91284691803108</v>
+        <v>-12.01196437997144</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.606434744704145</v>
+        <v>-1.646081729480292</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.652536687812756</v>
+        <v>-3.751654149753124</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9675384341343798</v>
+        <v>0.9080679569701591</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.14487583776734</v>
+        <v>-12.24399329970771</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.696552583969535</v>
+        <v>-1.736199568745682</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.714549385001179</v>
+        <v>-3.813666846941547</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9330245444504408</v>
+        <v>0.8735540672862196</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.09286032379852</v>
+        <v>-12.19197778573889</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.671756042695609</v>
+        <v>-1.711403027471756</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.714549385001179</v>
+        <v>-3.813666846941547</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9370148801368416</v>
+        <v>0.8775444029726205</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.23453216552264</v>
+        <v>-12.33364962746301</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.729900006283999</v>
+        <v>-1.769546991060146</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.714549385001179</v>
+        <v>-3.813666846941547</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9355396532381</v>
+        <v>0.8760691760738788</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.33343890598192</v>
+        <v>-12.43255636792229</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.754409292302836</v>
+        <v>-1.794056277078984</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.813456125460454</v>
+        <v>-3.912573587400823</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8912490191274065</v>
+        <v>0.8317785419631858</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.13428679874482</v>
+        <v>-12.23340426068519</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.68779958305468</v>
+        <v>-1.727446567830827</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.648133599510641</v>
+        <v>-3.74725106145101</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9773914010506117</v>
+        <v>0.9179209238863906</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.90844164602541</v>
+        <v>-12.00755910796578</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.587882448930706</v>
+        <v>-1.627529433706854</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.606206923923478</v>
+        <v>-3.705324385863846</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.012126479439118</v>
+        <v>0.9526560022748973</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.62216683370271</v>
+        <v>-11.72128429564308</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.47223337944557</v>
+        <v>-1.511880364221718</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.606206923923478</v>
+        <v>-3.705324385863846</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.013265623995177</v>
+        <v>0.9537951468309562</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.675062121747</v>
+        <v>-11.77417958368737</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.490757720501176</v>
+        <v>-1.530404705277324</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.601251577835031</v>
+        <v>-3.7003690397754</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.018872605810353</v>
+        <v>0.9594021286461318</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.39115339081825</v>
+        <v>-11.49027085275862</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.371460523891041</v>
+        <v>-1.411107508667189</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.601251577835031</v>
+        <v>-3.7003690397754</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.024606310048989</v>
+        <v>0.9651358328847683</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.1441661406253</v>
+        <v>-11.24328360256567</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.282402886207725</v>
+        <v>-1.322049870983873</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.354264327642079</v>
+        <v>-3.453381789582448</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.163061397770895</v>
+        <v>1.103590920606674</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.88032927342123</v>
+        <v>-10.9794467353616</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.186751620639005</v>
+        <v>-1.226398605415153</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.354264327642079</v>
+        <v>-3.453381789582448</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.153177916457988</v>
+        <v>1.093707439293766</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.61308747255283</v>
+        <v>-10.7122049344932</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.081689460791019</v>
+        <v>-1.121336445567167</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.354264327642079</v>
+        <v>-3.453381789582448</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.151343355958614</v>
+        <v>1.091872878794393</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.33727830915235</v>
+        <v>-10.43639577109272</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9716661104042861</v>
+        <v>-1.011313095180434</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.265245019363346</v>
+        <v>-3.364362481303714</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.204454625952393</v>
+        <v>1.144984148788172</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.31332476817639</v>
+        <v>-10.41244223011676</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9614161878684091</v>
+        <v>-1.001063172644557</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.241291478387388</v>
+        <v>-3.340408940327757</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.219495256683461</v>
+        <v>1.16002477951924</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.04926482985359</v>
+        <v>-10.14838229179396</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8690525287010429</v>
+        <v>-0.9086995134771909</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.977231540064592</v>
+        <v>-3.076349002004961</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.364670903515387</v>
+        <v>1.305200426351166</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.342185206348756</v>
+        <v>-9.441302668289126</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5890077129594085</v>
+        <v>-0.6286546977355565</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.977231540064592</v>
+        <v>-3.076349002004961</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.361883869855086</v>
+        <v>1.302413392690865</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.302000907982565</v>
+        <v>-9.401118369922935</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5725903697250909</v>
+        <v>-0.612237354501239</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.937047241698401</v>
+        <v>-3.03616470363877</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.386338072762642</v>
+        <v>1.326867595598421</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.221931112444761</v>
+        <v>-9.321048574385131</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5411956302892125</v>
+        <v>-0.5808426150653605</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.856977446160597</v>
+        <v>-2.956094908100966</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.433746771306081</v>
+        <v>1.37427629414186</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.988449890215161</v>
+        <v>-9.087567352155531</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.43987871255952</v>
+        <v>-0.4795256973356681</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.623496223930999</v>
+        <v>-2.722613685871367</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.581759933481693</v>
+        <v>1.522289456317472</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.808741360071288</v>
+        <v>-8.907858822011658</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3708875108149301</v>
+        <v>-0.4105344955910781</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.566324719768303</v>
+        <v>-2.665442181708671</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.613170625666351</v>
+        <v>1.55370014850213</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.676465886440401</v>
+        <v>-8.775583348380771</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3226098346155482</v>
+        <v>-0.3622568193916962</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.434049246137417</v>
+        <v>-2.533166708077785</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.68790339659191</v>
+        <v>1.628432919427689</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.485866211767247</v>
+        <v>-8.584983673707617</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2435549040586498</v>
+        <v>-0.2832018888347978</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.243449571464264</v>
+        <v>-2.342567033404632</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.805078262083438</v>
+        <v>1.745607784919217</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.236866413083666</v>
+        <v>-8.335983875024036</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.131048643361559</v>
+        <v>-0.170695628137707</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.243449571464264</v>
+        <v>-2.342567033404632</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.817984603307097</v>
+        <v>1.758514126142876</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.34245640285677</v>
+        <v>-8.441573864797141</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3012605688700192</v>
+        <v>-0.3409075536461672</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.349039561237368</v>
+        <v>-2.448157023177737</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.626654679844016</v>
+        <v>1.567184202679795</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.361191304975367</v>
+        <v>-8.460308766915738</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2602101878403715</v>
+        <v>-0.2998571726165196</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.349039561237368</v>
+        <v>-2.448157023177737</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.675199021721102</v>
+        <v>1.615728544556881</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.084453130304555</v>
+        <v>-8.183570592244925</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1461359059860521</v>
+        <v>-0.1857828907622001</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.167222900127443</v>
+        <v>-2.266340362067811</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.787668030373052</v>
+        <v>1.728197553208831</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.140769120766286</v>
+        <v>-8.056678185809854</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1773762884242229</v>
+        <v>-0.14373991444165</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.223538890589175</v>
+        <v>-2.139447955632741</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.745164449842534</v>
+        <v>1.795619010816395</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.95318161285636</v>
+        <v>-7.869090677899928</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1093018973553455</v>
+        <v>-0.07566552337277255</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.223538890589175</v>
+        <v>-2.139447955632741</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.738203837747441</v>
+        <v>1.788658398721302</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.711033219402502</v>
+        <v>-7.62694228444607</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.002019814407340892</v>
+        <v>0.0356561883899138</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.223538890589175</v>
+        <v>-2.139447955632741</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.752666192128584</v>
+        <v>1.803120753102445</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.647803847634154</v>
+        <v>-7.563712912677722</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02184368357387534</v>
+        <v>0.05548005755644825</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.223538890589175</v>
+        <v>-2.139447955632741</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.747198312587779</v>
+        <v>1.79765287356164</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.461316155257148</v>
+        <v>-7.377225220300716</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.09393685453525435</v>
+        <v>0.1275732285178273</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.037051198212169</v>
+        <v>-1.952960263255735</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.85658902202456</v>
+        <v>1.90704358299842</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.440166956353704</v>
+        <v>-7.356076021397272</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1100975123339576</v>
+        <v>0.1437338863165305</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.015901999308725</v>
+        <v>-1.931811064352291</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.876979519603952</v>
+        <v>1.927434080577812</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.19640151437026</v>
+        <v>-7.112310579413828</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2033843974743861</v>
+        <v>0.2370207714569585</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.015901999308725</v>
+        <v>-1.931811064352291</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.872760227951002</v>
+        <v>1.923214788924863</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.932373447177</v>
+        <v>-6.848282512220567</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3111199382717063</v>
+        <v>0.3447563122542787</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.814036600492772</v>
+        <v>-1.729945665536338</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.99600378116059</v>
+        <v>2.046458342134451</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.682523053227925</v>
+        <v>-6.598432118271493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4038021708350379</v>
+        <v>0.4374385448176108</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.814036600492772</v>
+        <v>-1.729945665536338</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.988745856144293</v>
+        <v>2.039200417118153</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.378955564223946</v>
+        <v>-6.294864629267514</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5288282899572785</v>
+        <v>0.562464663939851</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.814036600492772</v>
+        <v>-1.729945665536338</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.992344979664941</v>
+        <v>2.042799540638802</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.305475655371932</v>
+        <v>-6.2213847204155</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5715477595526375</v>
+        <v>0.6051841335352104</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.740556691640758</v>
+        <v>-1.656465756684323</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.049760431030704</v>
+        <v>2.100214992004564</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.080442655703109</v>
+        <v>-5.996351720746677</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6605814370364635</v>
+        <v>0.6942178110190365</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.515523691971935</v>
+        <v>-1.431432757015501</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.183800708448294</v>
+        <v>2.234255269422155</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.865808278066702</v>
+        <v>-5.78171734311027</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.751129989145344</v>
+        <v>0.7847663631279165</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.300889314335528</v>
+        <v>-1.216798379379094</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.317276136084455</v>
+        <v>2.367730697058316</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.599207921092351</v>
+        <v>-5.515116986135919</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8389643907188802</v>
+        <v>0.8726007647014531</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.300889314335528</v>
+        <v>-1.216798379379094</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.298470394868251</v>
+        <v>2.348924955842112</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.35877742428749</v>
+        <v>-5.274686489331058</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9368796660657015</v>
+        <v>0.9705160400482744</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.060458817530668</v>
+        <v>-0.9763678825742335</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.444471769576045</v>
+        <v>2.494926330549905</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.115986616638045</v>
+        <v>-5.031895681681613</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.0379253029603</v>
+        <v>1.071561676942873</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.060458817530668</v>
+        <v>-0.9763678825742335</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.448401083410865</v>
+        <v>2.498855644384725</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.876381525030956</v>
+        <v>-4.792290590074524</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.134445923520476</v>
+        <v>1.168082297503048</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9934108698621732</v>
+        <v>-0.9093199349057389</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.489308435929302</v>
+        <v>2.539762996903162</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.633725936607792</v>
+        <v>-4.54963500165136</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.228506230109735</v>
+        <v>1.262142604092307</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9934108698621732</v>
+        <v>-0.9093199349057389</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.486306507149295</v>
+        <v>2.536761068123156</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.413705138570782</v>
+        <v>-4.32961420361435</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.318093586335153</v>
+        <v>1.351729960317726</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.852191024794193</v>
+        <v>-0.7681000898377587</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.572617451200697</v>
+        <v>2.623072012174558</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.214456508665973</v>
+        <v>-4.130365573709541</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.4136872210989</v>
+        <v>1.447323595081473</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.852191024794193</v>
+        <v>-0.7681000898377587</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.588511634002521</v>
+        <v>2.638966194976381</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.054941405146603</v>
+        <v>-3.970850470190171</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.47863910694695</v>
+        <v>1.512275480929522</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.692675921274823</v>
+        <v>-0.6085849863183888</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.685366540554444</v>
+        <v>2.735821101528305</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.448691006751615</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.804301148820723</v>
+        <v>3.076462942500273</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.054941405146603</v>
+        <v>-3.824051381995078</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.47863910694695</v>
+        <v>1.546485965388494</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.692675921274823</v>
+        <v>-0.4617858981232962</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.797364945807091</v>
+        <v>2.799391403626295</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240412.xlsx
+++ b/tame_output/ON/bt/strategyON_20240412.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-23.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.6%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.4%</t>
+          <t>139.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-716.7%</t>
+          <t>-713.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-57.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5723.5%</t>
+          <t>5770.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-544.0%</t>
+          <t>-559.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-280.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>134.7%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-221.6%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.6%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.2%</t>
+          <t>-291.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-166.1%</t>
+          <t>-198.8%</t>
         </is>
       </c>
     </row>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213499</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382332</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178247</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207817</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776683</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1582294085368</v>
+        <v>-11.13041443427842</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.321739097310355</v>
+        <v>-1.310613107607004</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.19954818242663</v>
+        <v>-3.23013311374356</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.222180180962133</v>
+        <v>1.203829222171975</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.08475957686935</v>
+        <v>-11.05694460261097</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.276979463149954</v>
+        <v>-1.265853473446603</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.126078350759181</v>
+        <v>-3.156663282076112</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.281633781456023</v>
+        <v>1.263282822665865</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.25988399425589</v>
+        <v>-11.23206901999751</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.332474009357055</v>
+        <v>-1.321348019653703</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.301202768145725</v>
+        <v>-3.331787699462656</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.191114351771614</v>
+        <v>1.172763392981456</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.49433608827038</v>
+        <v>-11.466521114012</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.433474011864446</v>
+        <v>-1.422348022161095</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.301202768145725</v>
+        <v>-3.331787699462656</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.183895186870018</v>
+        <v>1.16554422807986</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.78213993280762</v>
+        <v>-11.75432495854924</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.555267740453318</v>
+        <v>-1.544141750749967</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.589006612682963</v>
+        <v>-3.619591543999894</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.004540689373699</v>
+        <v>0.9861897305835408</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.01196437997144</v>
+        <v>-11.98414940571307</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.646081729480292</v>
+        <v>-1.634955739776941</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.751654149753124</v>
+        <v>-3.782239081070054</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9080679569701591</v>
+        <v>0.8897169981800008</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.24399329970771</v>
+        <v>-12.21617832544933</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.736199568745682</v>
+        <v>-1.725073579042331</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.813666846941547</v>
+        <v>-3.844251778258478</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8735540672862196</v>
+        <v>0.8552031084960614</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.19197778573889</v>
+        <v>-12.16416281148051</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.711403027471756</v>
+        <v>-1.700277037768405</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.813666846941547</v>
+        <v>-3.844251778258478</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8775444029726205</v>
+        <v>0.8591934441824622</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.33364962746301</v>
+        <v>-12.30583465320463</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.769546991060146</v>
+        <v>-1.758421001356795</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.813666846941547</v>
+        <v>-3.844251778258478</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8760691760738788</v>
+        <v>0.8577182172837206</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.43255636792229</v>
+        <v>-12.40474139366391</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.794056277078984</v>
+        <v>-1.782930287375633</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.912573587400823</v>
+        <v>-3.943158518717753</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8317785419631858</v>
+        <v>0.8134275831730275</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.23340426068519</v>
+        <v>-12.20558928642681</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.727446567830827</v>
+        <v>-1.716320578127476</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.74725106145101</v>
+        <v>-3.77783599276794</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9179209238863906</v>
+        <v>0.8995699650962323</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.00755910796578</v>
+        <v>-11.9797441337074</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.627529433706854</v>
+        <v>-1.616403444003502</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.705324385863846</v>
+        <v>-3.735909317180776</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9526560022748973</v>
+        <v>0.9343050434847391</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.72128429564308</v>
+        <v>-11.6934693213847</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.511880364221718</v>
+        <v>-1.500754374518366</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.705324385863846</v>
+        <v>-3.735909317180776</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9537951468309562</v>
+        <v>0.935444188040798</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.77417958368737</v>
+        <v>-11.74636460942899</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.530404705277324</v>
+        <v>-1.519278715573972</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.7003690397754</v>
+        <v>-3.73095397109233</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9594021286461318</v>
+        <v>0.9410511698559736</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.49027085275862</v>
+        <v>-11.46245587850024</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.411107508667189</v>
+        <v>-1.399981518963837</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.7003690397754</v>
+        <v>-3.73095397109233</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9651358328847683</v>
+        <v>0.9467848740946101</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.24328360256567</v>
+        <v>-11.21546862830729</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.322049870983873</v>
+        <v>-1.310923881280521</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.453381789582448</v>
+        <v>-3.483966720899378</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.103590920606674</v>
+        <v>1.085239961816516</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.9794467353616</v>
+        <v>-10.95163176110322</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.226398605415153</v>
+        <v>-1.215272615711801</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.453381789582448</v>
+        <v>-3.483966720899378</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.093707439293766</v>
+        <v>1.075356480503608</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.7122049344932</v>
+        <v>-10.68438996023482</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.121336445567167</v>
+        <v>-1.110210455863815</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.453381789582448</v>
+        <v>-3.483966720899378</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.091872878794393</v>
+        <v>1.073521920004235</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.43639577109272</v>
+        <v>-10.40858079683434</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.011313095180434</v>
+        <v>-1.000187105477082</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.364362481303714</v>
+        <v>-3.394947412620644</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.144984148788172</v>
+        <v>1.126633189998014</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.41244223011676</v>
+        <v>-10.38462725585838</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.001063172644557</v>
+        <v>-0.9899371829412051</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.340408940327757</v>
+        <v>-3.370993871644687</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.16002477951924</v>
+        <v>1.141673820729082</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.14838229179396</v>
+        <v>-10.12056731753558</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9086995134771909</v>
+        <v>-0.8975735237738389</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.076349002004961</v>
+        <v>-3.106933933321891</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.305200426351166</v>
+        <v>1.286849467561008</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.441302668289126</v>
+        <v>-9.413487694030746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6286546977355565</v>
+        <v>-0.6175287080322045</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.076349002004961</v>
+        <v>-3.106933933321891</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.302413392690865</v>
+        <v>1.284062433900707</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.401118369922935</v>
+        <v>-9.373303395664555</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.612237354501239</v>
+        <v>-0.601111364797887</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.03616470363877</v>
+        <v>-3.0667496349557</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.326867595598421</v>
+        <v>1.308516636808263</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.321048574385131</v>
+        <v>-9.293233600126751</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5808426150653605</v>
+        <v>-0.5697166253620085</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.956094908100966</v>
+        <v>-2.986679839417896</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.37427629414186</v>
+        <v>1.355925335351702</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.087567352155531</v>
+        <v>-9.059752377897151</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4795256973356681</v>
+        <v>-0.4683997076323161</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.722613685871367</v>
+        <v>-2.753198617188298</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.522289456317472</v>
+        <v>1.503938497527313</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.907858822011658</v>
+        <v>-8.880043847753278</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4105344955910781</v>
+        <v>-0.3994085058877261</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.665442181708671</v>
+        <v>-2.696027113025602</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.55370014850213</v>
+        <v>1.535349189711972</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.775583348380771</v>
+        <v>-8.747768374122391</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3622568193916962</v>
+        <v>-0.3511308296883442</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.533166708077785</v>
+        <v>-2.563751639394715</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.628432919427689</v>
+        <v>1.610081960637531</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.584983673707617</v>
+        <v>-8.557168699449237</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2832018888347978</v>
+        <v>-0.2720758991314458</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.342567033404632</v>
+        <v>-2.373151964721563</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.745607784919217</v>
+        <v>1.727256826129059</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.335983875024036</v>
+        <v>-8.308168900765656</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.170695628137707</v>
+        <v>-0.159569638434355</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.342567033404632</v>
+        <v>-2.373151964721563</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.758514126142876</v>
+        <v>1.740163167352718</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.441573864797141</v>
+        <v>-8.413758890538761</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3409075536461672</v>
+        <v>-0.3297815639428152</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.448157023177737</v>
+        <v>-2.478741954494667</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.567184202679795</v>
+        <v>1.548833243889636</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.460308766915738</v>
+        <v>-8.432493792657358</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2998571726165196</v>
+        <v>-0.2887311829131676</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.448157023177737</v>
+        <v>-2.478741954494667</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.615728544556881</v>
+        <v>1.597377585766723</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.183570592244925</v>
+        <v>-8.155755617986545</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1857828907622001</v>
+        <v>-0.1746569010588481</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.266340362067811</v>
+        <v>-2.296925293384741</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.728197553208831</v>
+        <v>1.709846594418673</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.056678185809854</v>
+        <v>-8.028863211551474</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.14373991444165</v>
+        <v>-0.132613924738298</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.139447955632741</v>
+        <v>-2.170032886949671</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.795619010816395</v>
+        <v>1.777268052026237</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.869090677899928</v>
+        <v>-7.841275703641548</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07566552337277255</v>
+        <v>-0.06453953366942056</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.139447955632741</v>
+        <v>-2.170032886949671</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.788658398721302</v>
+        <v>1.770307439931143</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.62694228444607</v>
+        <v>-7.59912731018769</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0356561883899138</v>
+        <v>0.04678217809326579</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.139447955632741</v>
+        <v>-2.170032886949671</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.803120753102445</v>
+        <v>1.784769794312286</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.563712912677722</v>
+        <v>-7.535897938419342</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05548005755644825</v>
+        <v>0.06660604725980024</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.139447955632741</v>
+        <v>-2.170032886949671</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.79765287356164</v>
+        <v>1.779301914771481</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.377225220300716</v>
+        <v>-7.349410246042336</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1275732285178273</v>
+        <v>0.1386992182211793</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.952960263255735</v>
+        <v>-1.983545194572665</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.90704358299842</v>
+        <v>1.888692624208262</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.356076021397272</v>
+        <v>-7.328261047138892</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1437338863165305</v>
+        <v>0.1548598760198825</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.931811064352291</v>
+        <v>-1.962395995669222</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.927434080577812</v>
+        <v>1.909083121787654</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.112310579413828</v>
+        <v>-7.084495605155448</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2370207714569585</v>
+        <v>0.2481467611603105</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.931811064352291</v>
+        <v>-1.962395995669222</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.923214788924863</v>
+        <v>1.904863830134705</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.848282512220567</v>
+        <v>-6.820467537962188</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3447563122542787</v>
+        <v>0.3558823019576307</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.729945665536338</v>
+        <v>-1.760530596853268</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.046458342134451</v>
+        <v>2.028107383344293</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.598432118271493</v>
+        <v>-6.570617144013113</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4374385448176108</v>
+        <v>0.4485645345209628</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.729945665536338</v>
+        <v>-1.760530596853268</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.039200417118153</v>
+        <v>2.020849458327995</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.294864629267514</v>
+        <v>-6.267049655009134</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.562464663939851</v>
+        <v>0.5735906536432029</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.729945665536338</v>
+        <v>-1.760530596853268</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.042799540638802</v>
+        <v>2.024448581848644</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.2213847204155</v>
+        <v>-6.19356974615712</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6051841335352104</v>
+        <v>0.6163101232385624</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.656465756684323</v>
+        <v>-1.687050688001254</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.100214992004564</v>
+        <v>2.081864033214406</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.996351720746677</v>
+        <v>-5.968536746488297</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6942178110190365</v>
+        <v>0.7053438007223884</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.431432757015501</v>
+        <v>-1.462017688332431</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.234255269422155</v>
+        <v>2.215904310631997</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.78171734311027</v>
+        <v>-5.75390236885189</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7847663631279165</v>
+        <v>0.7958923528312685</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.216798379379094</v>
+        <v>-1.247383310696024</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.367730697058316</v>
+        <v>2.349379738268158</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.515116986135919</v>
+        <v>-5.487302011877539</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8726007647014531</v>
+        <v>0.8837267544048051</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.216798379379094</v>
+        <v>-1.247383310696024</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.348924955842112</v>
+        <v>2.330573997051954</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.274686489331058</v>
+        <v>-5.246871515072678</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9705160400482744</v>
+        <v>0.9816420297516264</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9763678825742335</v>
+        <v>-1.006952813891164</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.494926330549905</v>
+        <v>2.476575371759747</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.031895681681613</v>
+        <v>-5.004080707423233</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.071561676942873</v>
+        <v>1.082687666646225</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9763678825742335</v>
+        <v>-1.006952813891164</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.498855644384725</v>
+        <v>2.480504685594567</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.792290590074524</v>
+        <v>-4.764475615816144</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.168082297503048</v>
+        <v>1.1792082872064</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9093199349057389</v>
+        <v>-0.9399048662226693</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.539762996903162</v>
+        <v>2.521412038113004</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.54963500165136</v>
+        <v>-4.52182002739298</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.262142604092307</v>
+        <v>1.273268593795659</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9093199349057389</v>
+        <v>-0.9399048662226693</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.536761068123156</v>
+        <v>2.518410109332998</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.32961420361435</v>
+        <v>-4.30179922935597</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.351729960317726</v>
+        <v>1.362855950021078</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7681000898377587</v>
+        <v>-0.7986850211546891</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.623072012174558</v>
+        <v>2.6047210533844</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.130365573709541</v>
+        <v>-4.102550599451161</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.447323595081473</v>
+        <v>1.458449584784825</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7681000898377587</v>
+        <v>-0.7986850211546891</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.638966194976381</v>
+        <v>2.620615236186223</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.970850470190171</v>
+        <v>-3.943035495931791</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.512275480929522</v>
+        <v>1.523401470632874</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6085849863183888</v>
+        <v>-0.6391699176353192</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.735821101528305</v>
+        <v>2.717470142738147</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.448691006751615</v>
+        <v>3.743875789147443</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.076462942500273</v>
+        <v>2.877305722027706</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.824051381995078</v>
+        <v>-3.978953926318538</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.546485965388494</v>
+        <v>1.285367727186544</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4617858981232962</v>
+        <v>-0.6750883480220657</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.799391403626295</v>
+        <v>2.472252713214467</v>
       </c>
     </row>
   </sheetData>
